--- a/data/cns_capability.xlsx
+++ b/data/cns_capability.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oburdash\dev\repos\standard_inputs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888F7C5A-1311-4B74-9E08-DC6DAFBCDF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89484856-33B2-42CC-B885-0E893F051B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" firstSheet="5" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="18240" tabRatio="857" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nav_total" sheetId="1" r:id="rId1"/>
@@ -55,43 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="137">
-  <si>
-    <t>A – GBAS landing system</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>–</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> LPV (APV with SBAS)</t>
-    </r>
-  </si>
-  <si>
-    <t>D – RNAV 1</t>
-  </si>
-  <si>
-    <t>O –- Basic RNP 1</t>
-  </si>
-  <si>
-    <t>S – RNP APCH</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="132">
   <si>
     <t>capability</t>
   </si>
@@ -108,30 +72,12 @@
     <t>Barcelona</t>
   </si>
   <si>
-    <t>Frankfurt Main</t>
-  </si>
-  <si>
-    <t>Istanbul/New airport</t>
-  </si>
-  <si>
-    <t>London/Gatwick</t>
-  </si>
-  <si>
-    <t>London/Heathrow</t>
-  </si>
-  <si>
     <t>Madrid Barajas</t>
   </si>
   <si>
-    <t>Paris Ch de Gaulle</t>
-  </si>
-  <si>
     <t>Rome Fiumicino</t>
   </si>
   <si>
-    <t>Schiphol Amsterdam</t>
-  </si>
-  <si>
     <t>airport</t>
   </si>
   <si>
@@ -345,9 +291,6 @@
     <t xml:space="preserve">Frankfurt Main </t>
   </si>
   <si>
-    <t>Amsterdam Schiphol</t>
-  </si>
-  <si>
     <t>Paris Ch. de Gaulle</t>
   </si>
   <si>
@@ -360,9 +303,6 @@
     <t>Munich</t>
   </si>
   <si>
-    <t>Istanbul Main</t>
-  </si>
-  <si>
     <t>B1</t>
   </si>
   <si>
@@ -381,39 +321,9 @@
     <t>V2</t>
   </si>
   <si>
-    <t>B737-800</t>
-  </si>
-  <si>
-    <t>B777-300ER</t>
-  </si>
-  <si>
-    <t>CRJ9</t>
-  </si>
-  <si>
-    <t>ATR72-600</t>
-  </si>
-  <si>
-    <t>A330-300</t>
-  </si>
-  <si>
-    <t>E170</t>
-  </si>
-  <si>
     <t>Palma de Mallorca</t>
   </si>
   <si>
-    <t>A321 NEO</t>
-  </si>
-  <si>
-    <t>B737 Max</t>
-  </si>
-  <si>
-    <t>B787 Dreamliner</t>
-  </si>
-  <si>
-    <t>ATR72-500</t>
-  </si>
-  <si>
     <t>EBBR</t>
   </si>
   <si>
@@ -429,18 +339,6 @@
     <t>EDDM</t>
   </si>
   <si>
-    <t>EGCC</t>
-  </si>
-  <si>
-    <t>EGKK</t>
-  </si>
-  <si>
-    <t>EGLL</t>
-  </si>
-  <si>
-    <t>EGSS</t>
-  </si>
-  <si>
     <t>EHAM</t>
   </si>
   <si>
@@ -486,14 +384,83 @@
     <t>LSZH</t>
   </si>
   <si>
-    <t>LTFM</t>
+    <t>A - GBAS landing system</t>
+  </si>
+  <si>
+    <t>B - LPV (APV with SBAS)</t>
+  </si>
+  <si>
+    <t>RNAV 1 - Any means (any Dx)</t>
+  </si>
+  <si>
+    <t>RNP 1 (any Ox)</t>
+  </si>
+  <si>
+    <t>RNP APCH (S1 or S2)</t>
+  </si>
+  <si>
+    <t>Frankfurt</t>
+  </si>
+  <si>
+    <t>London Heathrow</t>
+  </si>
+  <si>
+    <t>Amsterdam</t>
+  </si>
+  <si>
+    <t>Paris Charles de Gaulle</t>
+  </si>
+  <si>
+    <t>Athens</t>
+  </si>
+  <si>
+    <t>Istanbul</t>
+  </si>
+  <si>
+    <t>Antalya</t>
+  </si>
+  <si>
+    <t>LGAV</t>
+  </si>
+  <si>
+    <t>EDDH</t>
+  </si>
+  <si>
+    <t>EFHK</t>
+  </si>
+  <si>
+    <t>LPPT</t>
+  </si>
+  <si>
+    <t>LFLL</t>
+  </si>
+  <si>
+    <t>LEMG</t>
+  </si>
+  <si>
+    <t>LIML</t>
+  </si>
+  <si>
+    <t>LKPR</t>
+  </si>
+  <si>
+    <t>EDDS</t>
+  </si>
+  <si>
+    <t>EPWA</t>
+  </si>
+  <si>
+    <t>LSGG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00000"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -502,17 +469,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -532,14 +493,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -827,68 +792,68 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="B2">
-        <v>2029678</v>
-      </c>
-      <c r="C2">
-        <v>0.10970000000000001</v>
+        <v>2710550</v>
+      </c>
+      <c r="C2" s="1">
+        <v>0.12182165064055749</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="B3">
-        <v>1856684</v>
-      </c>
-      <c r="C3">
-        <v>0.1003</v>
+        <v>2813308</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.12643995658456236</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="B4">
-        <v>17931330</v>
-      </c>
-      <c r="C4">
-        <v>0.96879999999999999</v>
+        <v>21826400</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.98095518457178943</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="B5">
-        <v>15712410</v>
-      </c>
-      <c r="C5">
-        <v>0.84889999999999999</v>
+        <v>19990936</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.89846297665408992</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>113</v>
       </c>
       <c r="B6">
-        <v>17295534</v>
-      </c>
-      <c r="C6">
-        <v>0.93440000000000001</v>
+        <v>21372218</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0.96054264802709199</v>
       </c>
     </row>
   </sheetData>
@@ -905,184 +870,184 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="115.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B2">
-        <v>4841403</v>
+        <v>12882160</v>
       </c>
       <c r="C2">
-        <v>0.52300000000000002</v>
+        <v>0.57896957998035969</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B3">
-        <v>1437964</v>
+        <v>2519656</v>
       </c>
       <c r="C3">
-        <v>0.155</v>
+        <v>0.11324220286155375</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B4">
-        <v>274513</v>
+        <v>751908</v>
       </c>
       <c r="C4">
-        <v>0.03</v>
+        <v>3.3793390156920289E-2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B5">
-        <v>2645524</v>
+        <v>6026698</v>
       </c>
       <c r="C5">
-        <v>0.28599999999999998</v>
+        <v>0.27086100543142405</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B6">
-        <v>2729</v>
+        <v>8490</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>3.8157046132273264E-4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B7">
-        <v>975</v>
+        <v>6486</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2.9150365278436327E-4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B8">
-        <v>3512</v>
+        <v>1946</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>8.7460084538755912E-5</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B9">
-        <v>122008</v>
+        <v>137556</v>
       </c>
       <c r="C9">
-        <v>1.2999999999999999E-2</v>
+        <v>6.1822504567384936E-3</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B10">
-        <v>88646</v>
+        <v>292710</v>
       </c>
       <c r="C10">
-        <v>0.01</v>
+        <v>1.3155416929773508E-2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B11">
-        <v>7409392</v>
+        <v>19255924</v>
       </c>
       <c r="C11">
-        <v>0.80100000000000005</v>
+        <v>0.86542895216436744</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B12">
-        <v>329079</v>
+        <v>1092596</v>
       </c>
       <c r="C12">
-        <v>3.5999999999999997E-2</v>
+        <v>4.9105107156580965E-2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B13">
-        <v>44076</v>
+        <v>152978</v>
       </c>
       <c r="C13">
-        <v>5.0000000000000001E-3</v>
+        <v>6.8753693795322729E-3</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B14">
-        <v>9195</v>
+        <v>34236</v>
       </c>
       <c r="C14">
-        <v>1E-3</v>
+        <v>1.5386862560477119E-3</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B15">
-        <v>64899</v>
+        <v>185124</v>
       </c>
       <c r="C15">
-        <v>7.0000000000000001E-3</v>
+        <v>8.3201236845594304E-3</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B16">
-        <v>6092</v>
+        <v>21190</v>
       </c>
       <c r="C16">
-        <v>1E-3</v>
+        <v>9.5235313020361663E-4</v>
       </c>
     </row>
   </sheetData>
@@ -1103,115 +1068,115 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F1" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="G1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J1" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B2">
-        <v>0.877</v>
+        <v>0.4250064087802462</v>
       </c>
       <c r="C2">
-        <v>6.9000000000000006E-2</v>
+        <v>0.48192072230212074</v>
       </c>
       <c r="D2">
-        <v>7.0000000000000001E-3</v>
+        <v>2.8815613961147585E-2</v>
       </c>
       <c r="E2">
-        <v>4.2999999999999997E-2</v>
+        <v>6.4880753238063374E-2</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1.7379743040499146E-5</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>4.0000000000000001E-3</v>
+        <v>2.0203951284580258E-4</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>4.7142552997353932E-4</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B3">
-        <v>0.75700000000000001</v>
+        <v>0.3581881387417199</v>
       </c>
       <c r="C3">
-        <v>0.17499999999999999</v>
+        <v>0.52419976227309928</v>
       </c>
       <c r="D3">
-        <v>1.2E-2</v>
+        <v>2.4432710743702925E-2</v>
       </c>
       <c r="E3">
-        <v>5.6000000000000001E-2</v>
+        <v>9.6563114102939329E-2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>5.9730377077870494E-6</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2.687866968504172E-5</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>5.9730377077870494E-6</v>
       </c>
       <c r="I3">
-        <v>1E-3</v>
+        <v>7.6753534545063583E-4</v>
       </c>
       <c r="J3">
-        <v>3.0000000000000001E-3</v>
+        <v>1.8456686517061983E-3</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B4">
-        <v>0.53</v>
+        <v>0.57940629367861707</v>
       </c>
       <c r="C4">
-        <v>0.42299999999999999</v>
+        <v>5.2171666989536923E-2</v>
       </c>
       <c r="D4">
-        <v>8.0000000000000002E-3</v>
+        <v>1.5706075584967994E-2</v>
       </c>
       <c r="E4">
-        <v>3.9E-2</v>
+        <v>0.35359917011929537</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1223,158 +1188,158 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>2E-3</v>
+        <v>6.2491016916318276E-5</v>
       </c>
       <c r="J4">
-        <v>4.0000000000000001E-3</v>
+        <v>2.0449143768916551E-2</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="B5">
-        <v>0.41699999999999998</v>
+        <v>0.81541344767228419</v>
       </c>
       <c r="C5">
-        <v>0.51800000000000002</v>
+        <v>0.11652472329662886</v>
       </c>
       <c r="D5">
-        <v>1.4E-2</v>
+        <v>7.4314909428704135E-3</v>
       </c>
       <c r="E5">
-        <v>5.1999999999999998E-2</v>
+        <v>6.0883868756300238E-2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>4.0564906893397454E-6</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>4.4621397582737198E-5</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>4.0000000000000001E-3</v>
+        <v>2.6570014015175333E-4</v>
       </c>
       <c r="J5">
-        <v>1E-3</v>
+        <v>8.6606076217403561E-3</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>0.57899999999999996</v>
+        <v>0.70172681848036644</v>
       </c>
       <c r="C6">
-        <v>8.8999999999999996E-2</v>
+        <v>6.5187328350474041E-2</v>
       </c>
       <c r="D6">
-        <v>1.6E-2</v>
+        <v>1.7686656301875915E-2</v>
       </c>
       <c r="E6">
-        <v>0.315</v>
+        <v>0.21717285089943658</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>2.2724942286960596E-4</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2.771334425239097E-6</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3.8798681953347359E-5</v>
       </c>
       <c r="I6">
-        <v>5.0000000000000001E-3</v>
+        <v>3.9630082280919083E-4</v>
       </c>
       <c r="J6">
-        <v>2.1999999999999999E-2</v>
+        <v>2.2447808844436685E-3</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B7">
-        <v>0.34399999999999997</v>
+        <v>0.47476107460136541</v>
       </c>
       <c r="C7">
-        <v>0.16600000000000001</v>
+        <v>8.0093689862413331E-2</v>
       </c>
       <c r="D7">
-        <v>6.0999999999999999E-2</v>
+        <v>6.378849676054997E-2</v>
       </c>
       <c r="E7">
-        <v>0.42899999999999999</v>
+        <v>0.38354577594751882</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>3.7141669935907404E-5</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2.3213543709942127E-6</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1.3928126225965277E-5</v>
       </c>
       <c r="I7">
-        <v>1E-3</v>
+        <v>5.0837660724773262E-4</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>9.0997091342973145E-4</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="B8">
-        <v>0.65400000000000003</v>
+        <v>0.63807733272748879</v>
       </c>
       <c r="C8">
-        <v>9.2999999999999999E-2</v>
+        <v>0.32256639104906298</v>
       </c>
       <c r="D8">
-        <v>1.4999999999999999E-2</v>
+        <v>2.8499013070819205E-2</v>
       </c>
       <c r="E8">
-        <v>0.23799999999999999</v>
+        <v>4.589481231670943E-2</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1.6674621850841338E-5</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>1E-3</v>
+        <v>1.729992017024789E-4</v>
       </c>
       <c r="J8">
-        <v>2E-3</v>
+        <v>7.6536514295361749E-3</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="B9">
-        <v>0.31900000000000001</v>
+        <v>0.24598736369974772</v>
       </c>
       <c r="C9">
-        <v>0.57599999999999996</v>
+        <v>4.9254975812769997E-2</v>
       </c>
       <c r="D9">
-        <v>2.1999999999999999E-2</v>
+        <v>1.2003766451269739E-2</v>
       </c>
       <c r="E9">
-        <v>8.3000000000000004E-2</v>
+        <v>0.69409443442133945</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1.3944495158960057E-3</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1383,74 +1348,74 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>2E-3</v>
+        <v>1.053025021024561E-3</v>
       </c>
       <c r="J9">
-        <v>1E-3</v>
+        <v>6.3720592569165412E-3</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>107</v>
+        <v>6</v>
       </c>
       <c r="B10">
-        <v>0.46100000000000002</v>
+        <v>0.69378555229207717</v>
       </c>
       <c r="C10">
-        <v>0.17399999999999999</v>
+        <v>7.3186600736141583E-2</v>
       </c>
       <c r="D10">
-        <v>4.8000000000000001E-2</v>
+        <v>1.6680918565887149E-2</v>
       </c>
       <c r="E10">
-        <v>0.317</v>
+        <v>0.21900521743441029</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>2.1997496622919532E-4</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1.8589433765847491E-5</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>5.5768301297542476E-5</v>
       </c>
       <c r="I10">
-        <v>2E-3</v>
+        <v>1.9209081558042409E-4</v>
       </c>
       <c r="J10">
-        <v>7.0000000000000001E-3</v>
+        <v>4.281766244066872E-3</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>119</v>
       </c>
       <c r="B11">
-        <v>0.82799999999999996</v>
+        <v>0.9262342684074335</v>
       </c>
       <c r="C11">
-        <v>1.7000000000000001E-2</v>
+        <v>3.1939176076217358E-2</v>
       </c>
       <c r="D11">
-        <v>1.4999999999999999E-2</v>
+        <v>6.0022641731357325E-3</v>
       </c>
       <c r="E11">
-        <v>0.13900000000000001</v>
+        <v>3.5329922371206773E-2</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>3.6756057398259234E-6</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>9.1890143495648082E-6</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>7.3512114796518468E-6</v>
       </c>
       <c r="I11">
-        <v>1E-3</v>
+        <v>5.3847624088449776E-4</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>3.4918254528346269E-5</v>
       </c>
     </row>
   </sheetData>
@@ -1468,255 +1433,255 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E1" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="F1" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="G1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2">
-        <v>0.91600000000000004</v>
-      </c>
-      <c r="C2">
-        <v>1.7000000000000001E-2</v>
-      </c>
-      <c r="D2">
-        <v>2E-3</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
+        <v>77</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.94196903798777332</v>
+      </c>
+      <c r="C2" s="2">
+        <v>3.1963519919357995E-2</v>
+      </c>
+      <c r="D2" s="2">
+        <v>5.5180684153584786E-3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2.1072938436605214E-4</v>
+      </c>
+      <c r="F2" s="2">
+        <v>5.4876538650376052E-3</v>
+      </c>
+      <c r="G2" s="2">
+        <v>2.2376419164642651E-4</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B3">
-        <v>0.95599999999999996</v>
-      </c>
-      <c r="C3">
-        <v>1.2999999999999999E-2</v>
-      </c>
-      <c r="D3">
-        <v>1E-3</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="G3">
-        <v>1E-3</v>
+        <v>81</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.95509768903171088</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2.0998214061725372E-2</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3.0581953063869693E-3</v>
+      </c>
+      <c r="E3" s="2">
+        <v>9.0790173158363148E-4</v>
+      </c>
+      <c r="F3" s="2">
+        <v>3.1149391646109461E-3</v>
+      </c>
+      <c r="G3" s="2">
+        <v>5.1368124286968627E-4</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B4">
-        <v>0.89800000000000002</v>
-      </c>
-      <c r="C4">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="D4">
-        <v>1E-3</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
+        <v>79</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.91091905538578832</v>
+      </c>
+      <c r="C4" s="2">
+        <v>7.9363591483724211E-2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2.874586778150641E-4</v>
+      </c>
+      <c r="E4" s="2">
+        <v>8.332135588842438E-6</v>
+      </c>
+      <c r="F4" s="2">
+        <v>4.1660677944212186E-5</v>
+      </c>
+      <c r="G4" s="2">
+        <v>8.332135588842438E-6</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B5">
-        <v>0.86199999999999999</v>
-      </c>
-      <c r="C5">
-        <v>3.1E-2</v>
-      </c>
-      <c r="D5">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
+        <v>116</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.97287830325107449</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1.8349535633228338E-2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1.2615686043846608E-3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>3.1640627376850014E-4</v>
+      </c>
+      <c r="F5" s="2">
+        <v>3.5433446171382675E-3</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1.0141226723349363E-4</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B6">
-        <v>0.86099999999999999</v>
-      </c>
-      <c r="C6">
-        <v>8.5999999999999993E-2</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>1E-3</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.95985167818156125</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1.7329154161020072E-2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3.1870345890249612E-4</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2.2170675401912774E-4</v>
+      </c>
+      <c r="F6" s="2">
+        <v>8.3167746101425293E-3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1.9676474419197588E-4</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7">
-        <v>0.88300000000000001</v>
-      </c>
-      <c r="C7">
-        <v>4.7E-2</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.90088513242166013</v>
+      </c>
+      <c r="C7" s="2">
+        <v>6.6068066752866292E-2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3.0409742260024188E-4</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2.3445679147041551E-4</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1.2344962544947224E-2</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3.4123909253614928E-4</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>0.92700000000000005</v>
-      </c>
-      <c r="C8">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="D8">
-        <v>1E-3</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
+        <v>78</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.95509941201114701</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2.5601797524235522E-2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1.1338742858572109E-3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3.1264915970327511E-5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>5.6443594965097932E-3</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1.2505966388131004E-5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B9">
-        <v>0.872</v>
-      </c>
-      <c r="C9">
-        <v>2.3E-2</v>
-      </c>
-      <c r="D9">
-        <v>2E-3</v>
-      </c>
-      <c r="E9">
-        <v>1E-3</v>
-      </c>
-      <c r="F9">
-        <v>1E-3</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
+        <v>118</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.84056554272118922</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1.8566304636904035E-2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>7.7629148307612687E-4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2.9110930615354756E-4</v>
+      </c>
+      <c r="F9" s="2">
+        <v>3.3208024553812096E-3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>2.0126075487158845E-4</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B10">
-        <v>0.81</v>
-      </c>
-      <c r="C10">
-        <v>4.9000000000000002E-2</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="G10">
-        <v>1E-3</v>
+        <v>6</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.94154552552329251</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3.3464079017486457E-2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1.1773308051703411E-4</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3.0982389609745822E-5</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1.6544596051604268E-3</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1.8589433765847491E-5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11">
-        <v>0.97299999999999998</v>
-      </c>
-      <c r="C11">
-        <v>7.0000000000000001E-3</v>
-      </c>
-      <c r="D11">
-        <v>1E-3</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
+        <v>119</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.96310978299223715</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1.9427414137849916E-2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1.0473638555633968E-2</v>
+      </c>
+      <c r="E11" s="2">
+        <v>8.8214537755822164E-5</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2.4883850858621499E-3</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1.0475476358503882E-4</v>
       </c>
     </row>
   </sheetData>
@@ -1734,63 +1699,63 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F1" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="G1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H1" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J1" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>0.46899999999999997</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="C2">
-        <v>3.1E-2</v>
+        <v>0.32590000000000002</v>
       </c>
       <c r="D2">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0.49</v>
+        <v>0.52029999999999998</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.127</v>
       </c>
       <c r="H2">
-        <v>1E-3</v>
+        <v>4.6699999999999998E-2</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1.9E-3</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1798,63 +1763,63 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>0.58599999999999997</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>0.19900000000000001</v>
+        <v>0.24660000000000001</v>
       </c>
       <c r="D3">
-        <v>6.0000000000000001E-3</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="E3">
-        <v>0.20799999999999999</v>
+        <v>0.621</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1162</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>9.7000000000000003E-3</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="J3">
-        <v>7.0000000000000001E-3</v>
+        <v>2.5999999999999999E-3</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>0.57799999999999996</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>0.28699999999999998</v>
+        <v>0.13669999999999999</v>
       </c>
       <c r="D4">
-        <v>7.3999999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>5.7000000000000002E-2</v>
+        <v>0.57369999999999999</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.19570000000000001</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>7.51E-2</v>
       </c>
       <c r="I4">
-        <v>4.0000000000000001E-3</v>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1862,63 +1827,63 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>0.70799999999999996</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>0.121</v>
+        <v>0.1512</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.17100000000000001</v>
+        <v>0.68400000000000005</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2.3E-3</v>
       </c>
       <c r="J5">
-        <v>0.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>0.64100000000000001</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0.253</v>
+        <v>0.74219999999999997</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="E6">
-        <v>0.106</v>
+        <v>9.3799999999999994E-2</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>7.8100000000000003E-2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>3.9100000000000003E-2</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1926,31 +1891,31 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>0.81200000000000006</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>6.4000000000000001E-2</v>
+        <v>0.51480000000000004</v>
       </c>
       <c r="D7">
-        <v>7.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0.11600000000000001</v>
+        <v>0.39639999999999997</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>6.2100000000000002E-2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1.4800000000000001E-2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1958,31 +1923,31 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>0.40200000000000002</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>5.7000000000000002E-2</v>
+        <v>9.4000000000000004E-3</v>
       </c>
       <c r="D8">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0.53</v>
+        <v>0.95030000000000003</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2.6499999999999999E-2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>9.4000000000000004E-3</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1990,31 +1955,31 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>0.42899999999999999</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>9.4E-2</v>
+        <v>4.0899999999999999E-2</v>
       </c>
       <c r="D9">
-        <v>8.1000000000000003E-2</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>0.39500000000000002</v>
+        <v>0.81420000000000003</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>3.4599999999999999E-2</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>0.1134</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2022,25 +1987,25 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B10">
-        <v>0.28499999999999998</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>0.46899999999999997</v>
+        <v>0.18479999999999999</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.246</v>
+        <v>0.42649999999999999</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.38390000000000002</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -2054,25 +2019,25 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>0.96399999999999997</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>2.4E-2</v>
+        <v>0.17849999999999999</v>
       </c>
       <c r="D11">
-        <v>1.2E-2</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>0.75170000000000003</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>6.83E-2</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -2081,33 +2046,33 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>0.10879999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="B12">
-        <v>0.92300000000000004</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>3.5000000000000003E-2</v>
+        <v>1.29E-2</v>
       </c>
       <c r="D12">
-        <v>1.4999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>2.5999999999999999E-2</v>
+        <v>0.97010000000000007</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2118,28 +2083,28 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="B13">
-        <v>0.88300000000000001</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>4.9000000000000002E-2</v>
+        <v>0.2</v>
       </c>
       <c r="D13">
-        <v>5.7000000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>1.0999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2150,28 +2115,28 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B14">
-        <v>0.70899999999999996</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>0.16</v>
+        <v>2.4E-2</v>
       </c>
       <c r="D14">
-        <v>8.8999999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>4.2999999999999997E-2</v>
+        <v>0.66400000000000003</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>0.14400000000000002</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2182,28 +2147,28 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0.55800000000000005</v>
+        <v>6.5700000000000008E-2</v>
       </c>
       <c r="D15">
-        <v>0.38100000000000001</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>0.06</v>
+        <v>0.86290000000000011</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3.4300000000000004E-2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>3.4300000000000004E-2</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2214,25 +2179,25 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="B16">
-        <v>0.33500000000000002</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>2.3E-2</v>
+        <v>2.1700000000000001E-2</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.64100000000000001</v>
+        <v>0.71740000000000004</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>0.26090000000000002</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2259,82 +2224,82 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="D1" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E1" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="F1" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="G1" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>0.96499999999999997</v>
+        <v>0.93340000000000001</v>
       </c>
       <c r="C2">
-        <v>3.0000000000000001E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D2">
-        <v>1E-3</v>
+        <v>1.9900000000000001E-2</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>2E-3</v>
+        <v>1.38E-2</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>0.86499999999999999</v>
+        <v>0.9345</v>
       </c>
       <c r="C3">
-        <v>1.2E-2</v>
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="D3">
-        <v>4.0000000000000001E-3</v>
+        <v>3.0499999999999999E-2</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>1.7000000000000001E-2</v>
+        <v>4.3499999999999997E-2</v>
       </c>
       <c r="G3">
-        <v>1E-3</v>
+        <v>1.9E-3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>0.79600000000000004</v>
+        <v>0.91690000000000005</v>
       </c>
       <c r="C4">
-        <v>7.3999999999999996E-2</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -2351,22 +2316,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>0.93400000000000005</v>
+        <v>0.95489999999999997</v>
       </c>
       <c r="C5">
-        <v>2.7E-2</v>
+        <v>1.8100000000000002E-2</v>
       </c>
       <c r="D5">
-        <v>1E-3</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>6.7999999999999996E-3</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -2374,22 +2339,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>0.91</v>
+        <v>0.66410000000000002</v>
       </c>
       <c r="C6">
-        <v>2E-3</v>
+        <v>1.5599999999999999E-2</v>
       </c>
       <c r="D6">
-        <v>1.2E-2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -2397,22 +2362,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>0.94099999999999995</v>
+        <v>0.53849999999999998</v>
       </c>
       <c r="C7">
-        <v>5.3999999999999999E-2</v>
+        <v>2.3699999999999999E-2</v>
       </c>
       <c r="D7">
-        <v>3.0000000000000001E-3</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>8.8999999999999999E-3</v>
       </c>
       <c r="F7">
-        <v>2E-3</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2420,22 +2385,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>0.97199999999999998</v>
+        <v>0.98629999999999995</v>
       </c>
       <c r="C8">
-        <v>1.0999999999999999E-2</v>
+        <v>2.5999999999999999E-3</v>
       </c>
       <c r="D8">
-        <v>4.9000000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>6.5000000000000002E-2</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -2443,13 +2408,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>0.56699999999999995</v>
+        <v>0.88029999999999997</v>
       </c>
       <c r="C9">
-        <v>1E-3</v>
+        <v>0.11020000000000001</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -2458,7 +2423,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2466,13 +2431,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B10">
-        <v>0.94899999999999995</v>
+        <v>0.96209999999999996</v>
       </c>
       <c r="C10">
-        <v>1E-3</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -2484,27 +2449,27 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>4.7000000000000002E-3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>102</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>0.996</v>
+        <v>0.83819999999999995</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>0.15060000000000001</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>2.8E-3</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2512,22 +2477,22 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="B12">
-        <v>0.64100000000000001</v>
+        <v>0.73109999999999997</v>
       </c>
       <c r="C12">
-        <v>0.35499999999999998</v>
+        <v>0.26790000000000003</v>
       </c>
       <c r="D12">
-        <v>1.4999999999999999E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="E12">
         <v>0</v>
       </c>
       <c r="F12">
-        <v>1.7000000000000001E-2</v>
+        <v>6.1800000000000001E-2</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2535,16 +2500,16 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="B13">
-        <v>0.89600000000000002</v>
+        <v>0.92</v>
       </c>
       <c r="C13">
-        <v>9.9000000000000005E-2</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -2558,10 +2523,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B14">
-        <v>0.97499999999999998</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -2581,10 +2546,10 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="B15">
-        <v>0.82699999999999996</v>
+        <v>0.98</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -2596,7 +2561,7 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2604,10 +2569,10 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c r="B16">
-        <v>0.58599999999999997</v>
+        <v>1</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -2640,222 +2605,222 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>114</v>
       </c>
       <c r="B2">
-        <v>5.1400000000000001E-2</v>
+        <v>8.8284749709975532E-2</v>
       </c>
       <c r="C2">
-        <v>3.4000000000000002E-2</v>
+        <v>4.2901895695472141E-2</v>
       </c>
       <c r="D2">
-        <v>0.99470000000000003</v>
+        <v>0.99893331827088938</v>
       </c>
       <c r="E2">
-        <v>0.94640000000000002</v>
+        <v>0.96879032643502361</v>
       </c>
       <c r="F2">
-        <v>0.98350000000000004</v>
+        <v>0.99513584441654035</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="B3">
-        <v>9.2899999999999996E-2</v>
+        <v>8.1409517438283591E-2</v>
       </c>
       <c r="C3">
-        <v>3.6999999999999998E-2</v>
+        <v>9.7202229137672541E-2</v>
       </c>
       <c r="D3">
-        <v>0.99890000000000001</v>
+        <v>0.99692388558048972</v>
       </c>
       <c r="E3">
-        <v>0.9456</v>
+        <v>0.96796659877313806</v>
       </c>
       <c r="F3">
-        <v>0.99229999999999996</v>
+        <v>0.9924889050824578</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="B4">
-        <v>0.39250000000000002</v>
+        <v>0.12918767927110478</v>
       </c>
       <c r="C4">
-        <v>9.4000000000000004E-3</v>
+        <v>8.0919617804940544E-2</v>
       </c>
       <c r="D4">
-        <v>0.98770000000000002</v>
+        <v>0.99975003593233469</v>
       </c>
       <c r="E4">
-        <v>0.95609999999999995</v>
+        <v>0.98540418148224529</v>
       </c>
       <c r="F4">
-        <v>0.9325</v>
+        <v>0.99754618606908585</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>116</v>
       </c>
       <c r="B5">
-        <v>5.8999999999999997E-2</v>
+        <v>5.304064400846184E-2</v>
       </c>
       <c r="C5">
-        <v>4.2900000000000001E-2</v>
+        <v>0.16887779213324761</v>
       </c>
       <c r="D5">
-        <v>0.99909999999999999</v>
+        <v>0.99908728959489856</v>
       </c>
       <c r="E5">
-        <v>0.94369999999999998</v>
+        <v>0.94029048529826365</v>
       </c>
       <c r="F5">
-        <v>0.99880000000000002</v>
+        <v>0.96058307997168568</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>0.11990000000000001</v>
+        <v>8.139409206927227E-2</v>
       </c>
       <c r="C6">
-        <v>3.5299999999999998E-2</v>
+        <v>4.4141814725208332E-2</v>
       </c>
       <c r="D6">
-        <v>0.99950000000000006</v>
+        <v>0.99698755947976514</v>
       </c>
       <c r="E6">
-        <v>0.94410000000000005</v>
+        <v>0.96508118624198735</v>
       </c>
       <c r="F6">
-        <v>0.99780000000000002</v>
+        <v>0.98555026230680332</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>7.7799999999999994E-2</v>
+        <v>0.14836472191335312</v>
       </c>
       <c r="C7">
-        <v>0.1115</v>
+        <v>0.15436310160800218</v>
       </c>
       <c r="D7">
-        <v>0.99199999999999999</v>
+        <v>0.99607923246739083</v>
       </c>
       <c r="E7">
-        <v>0.94389999999999996</v>
+        <v>0.96215031698093934</v>
       </c>
       <c r="F7">
-        <v>0.98109999999999997</v>
+        <v>0.98927534280600671</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="B8">
-        <v>4.9099999999999998E-2</v>
+        <v>8.7612631859783102E-2</v>
       </c>
       <c r="C8">
-        <v>0.1706</v>
+        <v>0.21469200931277629</v>
       </c>
       <c r="D8">
-        <v>0.99509999999999998</v>
+        <v>0.99921420844527908</v>
       </c>
       <c r="E8">
-        <v>0.9556</v>
+        <v>0.97234722398811102</v>
       </c>
       <c r="F8">
-        <v>0.98929999999999996</v>
+        <v>0.99464536205814857</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>118</v>
       </c>
       <c r="B9">
-        <v>3.3500000000000002E-2</v>
+        <v>4.1197357733803903E-2</v>
       </c>
       <c r="C9">
-        <v>6.7900000000000002E-2</v>
+        <v>5.993257764711802E-2</v>
       </c>
       <c r="D9">
-        <v>0.99909999999999999</v>
+        <v>0.98934755576001088</v>
       </c>
       <c r="E9">
-        <v>0.93920000000000003</v>
+        <v>0.94389497063749339</v>
       </c>
       <c r="F9">
-        <v>0.98009999999999997</v>
+        <v>0.96360774278875527</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B10">
-        <v>0.13639999999999999</v>
+        <v>0.16062200245380526</v>
       </c>
       <c r="C10">
-        <v>1.67E-2</v>
+        <v>0.16167230546157563</v>
       </c>
       <c r="D10">
-        <v>0.99909999999999999</v>
+        <v>0.99947639761559526</v>
       </c>
       <c r="E10">
-        <v>0.95140000000000002</v>
+        <v>0.97021972710711235</v>
       </c>
       <c r="F10">
-        <v>0.98950000000000005</v>
+        <v>0.99380662031701184</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="B11">
-        <v>3.2500000000000001E-2</v>
+        <v>0.41134990296400847</v>
       </c>
       <c r="C11">
-        <v>4.0099999999999997E-2</v>
+        <v>1.2803972594683605E-2</v>
       </c>
       <c r="D11">
-        <v>0.99870000000000003</v>
+        <v>0.99455459009644787</v>
       </c>
       <c r="E11">
-        <v>0.93500000000000005</v>
+        <v>0.9746125911550223</v>
       </c>
       <c r="F11">
-        <v>0.99009999999999998</v>
+        <v>0.96589956774876495</v>
       </c>
     </row>
   </sheetData>
@@ -2873,222 +2838,222 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>114</v>
       </c>
       <c r="B2">
-        <v>0.1041</v>
+        <v>8.4054301188717734E-2</v>
       </c>
       <c r="C2">
-        <v>0.12280000000000001</v>
+        <v>4.4758622306628214E-2</v>
       </c>
       <c r="D2">
-        <v>0.9879</v>
+        <v>0.99892147898056316</v>
       </c>
       <c r="E2">
-        <v>0.878</v>
+        <v>0.96590935734214911</v>
       </c>
       <c r="F2">
-        <v>0.98350000000000004</v>
+        <v>0.9946777332301705</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="B3">
-        <v>0.1231</v>
+        <v>8.3641419407842768E-2</v>
       </c>
       <c r="C3">
-        <v>0.1449</v>
+        <v>0.1050020539071634</v>
       </c>
       <c r="D3">
-        <v>0.99250000000000005</v>
+        <v>0.99601857996018583</v>
       </c>
       <c r="E3">
-        <v>0.87780000000000002</v>
+        <v>0.97187727114734412</v>
       </c>
       <c r="F3">
-        <v>0.98350000000000004</v>
+        <v>0.99481783423389258</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="B4">
-        <v>0.1313</v>
+        <v>0.12862901290848888</v>
       </c>
       <c r="C4">
-        <v>6.9500000000000006E-2</v>
+        <v>8.4864916742645999E-2</v>
       </c>
       <c r="D4">
-        <v>0.97450000000000003</v>
+        <v>0.99992801957867461</v>
       </c>
       <c r="E4">
-        <v>0.88749999999999996</v>
+        <v>0.98562790920869525</v>
       </c>
       <c r="F4">
-        <v>0.89780000000000004</v>
+        <v>0.99875233936369312</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>116</v>
       </c>
       <c r="B5">
-        <v>0.1232</v>
+        <v>5.9370529327610874E-2</v>
       </c>
       <c r="C5">
-        <v>4.2900000000000001E-2</v>
+        <v>0.17343973533619456</v>
       </c>
       <c r="D5">
-        <v>0.99819999999999998</v>
+        <v>0.99937410586552222</v>
       </c>
       <c r="E5">
-        <v>0.92889999999999995</v>
+        <v>0.97351126609442062</v>
       </c>
       <c r="F5">
-        <v>0.99329999999999996</v>
+        <v>0.99722818311874106</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>0.1933</v>
+        <v>6.8067027155505375E-2</v>
       </c>
       <c r="C6">
-        <v>5.9700000000000003E-2</v>
+        <v>5.1072553330560343E-2</v>
       </c>
       <c r="D6">
-        <v>0.99890000000000001</v>
+        <v>0.99637530453384038</v>
       </c>
       <c r="E6">
-        <v>0.94869999999999999</v>
+        <v>0.96244577812110044</v>
       </c>
       <c r="F6">
-        <v>0.99560000000000004</v>
+        <v>0.98713530215699086</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B7">
-        <v>0.1147</v>
+        <v>0.13782372488000422</v>
       </c>
       <c r="C7">
-        <v>0.15260000000000001</v>
+        <v>0.15884276596866923</v>
       </c>
       <c r="D7">
-        <v>0.98670000000000002</v>
+        <v>0.99709900311197852</v>
       </c>
       <c r="E7">
-        <v>0.87570000000000003</v>
+        <v>0.96239253125164825</v>
       </c>
       <c r="F7">
-        <v>0.98109999999999997</v>
+        <v>0.99132338203491743</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B8">
-        <v>9.4899999999999998E-2</v>
+        <v>9.2515227859808022E-2</v>
       </c>
       <c r="C8">
-        <v>0.1706</v>
+        <v>8.6615428771885064E-2</v>
       </c>
       <c r="D8">
-        <v>0.98440000000000005</v>
+        <v>0.99445099977676432</v>
       </c>
       <c r="E8">
-        <v>0.86119999999999997</v>
+        <v>0.95334375099658764</v>
       </c>
       <c r="F8">
-        <v>0.98019999999999996</v>
+        <v>0.99138948241222058</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="B9">
-        <v>0.1048</v>
+        <v>9.2499770072657042E-2</v>
       </c>
       <c r="C9">
-        <v>4.3799999999999999E-2</v>
+        <v>0.21546491308746435</v>
       </c>
       <c r="D9">
-        <v>0.99790000000000001</v>
+        <v>0.99917226156534533</v>
       </c>
       <c r="E9">
-        <v>0.91269999999999996</v>
+        <v>0.97252368251632482</v>
       </c>
       <c r="F9">
-        <v>0.98550000000000004</v>
+        <v>0.99620619884116623</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="B10">
-        <v>0.1343</v>
+        <v>7.9676062918548507E-2</v>
       </c>
       <c r="C10">
-        <v>3.6499999999999998E-2</v>
+        <v>1.95919638685563E-2</v>
       </c>
       <c r="D10">
-        <v>0.99650000000000005</v>
+        <v>0.99215075533406016</v>
       </c>
       <c r="E10">
-        <v>0.92669999999999997</v>
+        <v>0.96530135492913871</v>
       </c>
       <c r="F10">
-        <v>0.9889</v>
+        <v>0.96704563152156986</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="B11">
-        <v>7.9799999999999996E-2</v>
+        <v>0.41403725717021023</v>
       </c>
       <c r="C11">
-        <v>0.1424</v>
+        <v>1.7312218277553953E-2</v>
       </c>
       <c r="D11">
-        <v>0.99299999999999999</v>
+        <v>0.99503370696876625</v>
       </c>
       <c r="E11">
-        <v>0.88170000000000004</v>
+        <v>0.97371255335274642</v>
       </c>
       <c r="F11">
-        <v>0.98809999999999998</v>
+        <v>0.96272288483784751</v>
       </c>
     </row>
   </sheetData>
@@ -3106,27 +3071,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B2">
         <v>0.2145</v>
@@ -3146,7 +3111,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B3">
         <v>2.0799999999999999E-2</v>
@@ -3166,7 +3131,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>8.8999999999999999E-3</v>
@@ -3186,7 +3151,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>6.2199999999999998E-2</v>
@@ -3206,7 +3171,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3226,7 +3191,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3246,7 +3211,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>1.9E-3</v>
@@ -3266,7 +3231,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>2.8899999999999999E-2</v>
@@ -3286,7 +3251,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>5.7000000000000002E-3</v>
@@ -3306,7 +3271,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>0.1104</v>
@@ -3326,7 +3291,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>0.49869999999999998</v>
@@ -3346,7 +3311,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -3366,7 +3331,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -3386,7 +3351,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>4.1700000000000001E-2</v>
@@ -3406,7 +3371,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -3441,18 +3406,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>34120473</v>
@@ -3463,7 +3428,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>3682878</v>
@@ -3474,7 +3439,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>5836183</v>
@@ -3485,7 +3450,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B5">
         <v>914209</v>
@@ -3496,7 +3461,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>647681</v>
@@ -3507,7 +3472,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B7">
         <v>241932</v>
@@ -3518,7 +3483,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B8">
         <v>3547340</v>
@@ -3529,7 +3494,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B9">
         <v>616204</v>
@@ -3540,7 +3505,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B10">
         <v>35481</v>
@@ -3551,7 +3516,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B11">
         <v>329184</v>
@@ -3562,7 +3527,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B12">
         <v>262483</v>
@@ -3573,7 +3538,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B13">
         <v>906101</v>
@@ -3584,7 +3549,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B14">
         <v>8168841</v>
@@ -3600,7 +3565,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ECE6454-E65A-4392-8F47-6E55AFAC4506}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -3614,255 +3579,255 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B2">
-        <v>0.26769999999999999</v>
+        <v>0.26195091264047093</v>
       </c>
       <c r="C2">
-        <v>0.60619999999999996</v>
+        <v>0.44306298066543942</v>
       </c>
       <c r="D2">
-        <v>0.78739999999999999</v>
+        <v>0.87218158562431669</v>
       </c>
       <c r="E2">
-        <v>0.13750000000000001</v>
+        <v>0.19596641464496045</v>
       </c>
       <c r="F2">
-        <v>0.1431</v>
+        <v>0.1978304622048688</v>
       </c>
       <c r="G2">
-        <v>3.7499999999999999E-2</v>
+        <v>2.4870990730831998E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="B3">
-        <v>0.60499999999999998</v>
+        <v>0.81094522317797646</v>
       </c>
       <c r="C3">
-        <v>0.60440000000000005</v>
+        <v>0.86447670255984843</v>
       </c>
       <c r="D3">
-        <v>0.85970000000000002</v>
+        <v>0.87352470504242075</v>
       </c>
       <c r="E3">
-        <v>8.3400000000000002E-2</v>
+        <v>0.10488056677287912</v>
       </c>
       <c r="F3">
-        <v>4.3099999999999999E-2</v>
+        <v>0.18267594521303676</v>
       </c>
       <c r="G3">
-        <v>2.0299999999999999E-2</v>
+        <v>4.2897389039767808E-2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B4">
-        <v>0.81810000000000005</v>
+        <v>0.59084766717221449</v>
       </c>
       <c r="C4">
-        <v>0.81389999999999996</v>
+        <v>0.27087181846279912</v>
       </c>
       <c r="D4">
-        <v>0.74009999999999998</v>
+        <v>0.71241635099875644</v>
       </c>
       <c r="E4">
-        <v>0.1782</v>
+        <v>8.9273520553754593E-2</v>
       </c>
       <c r="F4">
-        <v>0.22919999999999999</v>
+        <v>6.3282131638909458E-2</v>
       </c>
       <c r="G4">
-        <v>3.2099999999999997E-2</v>
+        <v>2.3461253710745169E-2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B5">
-        <v>0.56310000000000004</v>
+        <v>0.26169433844090267</v>
       </c>
       <c r="C5">
-        <v>0.56359999999999999</v>
+        <v>0.45967292711113328</v>
       </c>
       <c r="D5">
-        <v>0.89300000000000002</v>
+        <v>0.89923428029830643</v>
       </c>
       <c r="E5">
-        <v>3.32E-2</v>
+        <v>0.11418729232312651</v>
       </c>
       <c r="F5">
-        <v>2.9100000000000001E-2</v>
+        <v>8.2239349068970194E-2</v>
       </c>
       <c r="G5">
-        <v>7.7999999999999996E-3</v>
+        <v>2.3808534047229081E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="B6">
-        <v>0.8034</v>
+        <v>0.61041354144498139</v>
       </c>
       <c r="C6">
-        <v>0.78059999999999996</v>
+        <v>0.79282959517889673</v>
       </c>
       <c r="D6">
-        <v>0.83340000000000003</v>
+        <v>0.90292390982751369</v>
       </c>
       <c r="E6">
-        <v>9.6600000000000005E-2</v>
+        <v>8.7109985310376684E-2</v>
       </c>
       <c r="F6">
-        <v>9.7699999999999995E-2</v>
+        <v>5.4367178294654116E-2</v>
       </c>
       <c r="G6">
-        <v>1.7899999999999999E-2</v>
+        <v>3.4201387987729231E-2</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="B7">
-        <v>0.37509999999999999</v>
+        <v>0.28868511954598097</v>
       </c>
       <c r="C7">
-        <v>0.433</v>
+        <v>0.68505437098609767</v>
       </c>
       <c r="D7">
-        <v>0.8256</v>
+        <v>0.84723983896762811</v>
       </c>
       <c r="E7">
-        <v>0.10630000000000001</v>
+        <v>0.15444468397647684</v>
       </c>
       <c r="F7">
-        <v>0.1007</v>
+        <v>0.14143475230995223</v>
       </c>
       <c r="G7">
-        <v>5.62E-2</v>
+        <v>4.3927946536450373E-2</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="B8">
-        <v>0.65129999999999999</v>
+        <v>0.32631632263443749</v>
       </c>
       <c r="C8">
-        <v>0.73829999999999996</v>
+        <v>0.80399124139919431</v>
       </c>
       <c r="D8">
-        <v>0.93559999999999999</v>
+        <v>0.87322237027686223</v>
       </c>
       <c r="E8">
-        <v>9.0499999999999997E-2</v>
+        <v>9.4014696371102852E-2</v>
       </c>
       <c r="F8">
-        <v>5.8099999999999999E-2</v>
+        <v>6.2607631827072185E-2</v>
       </c>
       <c r="G8">
-        <v>2.29E-2</v>
+        <v>3.0666791344258208E-2</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="B9">
-        <v>0.33550000000000002</v>
+        <v>0.38260443800309446</v>
       </c>
       <c r="C9">
-        <v>0.85409999999999997</v>
+        <v>0.81441861376055147</v>
       </c>
       <c r="D9">
-        <v>0.80769999999999997</v>
+        <v>0.82241328659002333</v>
       </c>
       <c r="E9">
-        <v>0.28849999999999998</v>
+        <v>0.17809201120272625</v>
       </c>
       <c r="F9">
-        <v>0.38590000000000002</v>
+        <v>7.8857791966156804E-2</v>
       </c>
       <c r="G9">
-        <v>3.9100000000000003E-2</v>
+        <v>0.14090757750837266</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="B10">
-        <v>0.16539999999999999</v>
+        <v>0.66132859208804695</v>
       </c>
       <c r="C10">
-        <v>0.12670000000000001</v>
+        <v>0.65982608477897486</v>
       </c>
       <c r="D10">
-        <v>0.8881</v>
+        <v>0.92039215440766775</v>
       </c>
       <c r="E10">
-        <v>7.3999999999999996E-2</v>
+        <v>5.3257623659481758E-2</v>
       </c>
       <c r="F10">
-        <v>5.7599999999999998E-2</v>
+        <v>3.4745481522290324E-2</v>
       </c>
       <c r="G10">
-        <v>6.2199999999999998E-2</v>
+        <v>1.8987936118397577E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B11">
-        <v>0.81240000000000001</v>
+        <v>0.79933348685439687</v>
       </c>
       <c r="C11">
-        <v>0.83509999999999995</v>
+        <v>0.88450943502800317</v>
       </c>
       <c r="D11">
-        <v>0.84670000000000001</v>
+        <v>0.77679196013086949</v>
       </c>
       <c r="E11">
-        <v>9.2499999999999999E-2</v>
+        <v>0.21150061046347429</v>
       </c>
       <c r="F11">
-        <v>0.16270000000000001</v>
+        <v>0.20172667747107359</v>
       </c>
       <c r="G11">
-        <v>3.3399999999999999E-2</v>
+        <v>5.6877381567913519E-2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -3870,22 +3835,22 @@
         <v>122</v>
       </c>
       <c r="B12">
-        <v>0.38200000000000001</v>
+        <v>0.64355703760892957</v>
       </c>
       <c r="C12">
-        <v>0.43309999999999998</v>
+        <v>0.68274293035900557</v>
       </c>
       <c r="D12">
-        <v>0.81120000000000003</v>
+        <v>0.83854196611171794</v>
       </c>
       <c r="E12">
-        <v>0.126</v>
+        <v>7.7952904651220095E-2</v>
       </c>
       <c r="F12">
-        <v>9.0200000000000002E-2</v>
+        <v>3.0800062421459842E-2</v>
       </c>
       <c r="G12">
-        <v>8.09E-2</v>
+        <v>1.6640247057567371E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -3893,22 +3858,22 @@
         <v>123</v>
       </c>
       <c r="B13">
-        <v>0.31090000000000001</v>
+        <v>0.83621623353734742</v>
       </c>
       <c r="C13">
-        <v>0.65939999999999999</v>
+        <v>0.87287467555356169</v>
       </c>
       <c r="D13">
-        <v>0.78610000000000002</v>
+        <v>0.72129970839875668</v>
       </c>
       <c r="E13">
-        <v>0.1103</v>
+        <v>0.13605280866472266</v>
       </c>
       <c r="F13">
-        <v>5.3800000000000001E-2</v>
+        <v>0.12953504021533629</v>
       </c>
       <c r="G13">
-        <v>4.1700000000000001E-2</v>
+        <v>1.2285705130259237E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -3916,22 +3881,22 @@
         <v>124</v>
       </c>
       <c r="B14">
-        <v>0.40539999999999998</v>
+        <v>0.36222387969090136</v>
       </c>
       <c r="C14">
-        <v>0.81069999999999998</v>
+        <v>0.83816119268362488</v>
       </c>
       <c r="D14">
-        <v>0.84319999999999995</v>
+        <v>0.93608145494913397</v>
       </c>
       <c r="E14">
-        <v>5.4300000000000001E-2</v>
+        <v>0.17581069009479372</v>
       </c>
       <c r="F14">
-        <v>5.8700000000000002E-2</v>
+        <v>0.13367388532822216</v>
       </c>
       <c r="G14">
-        <v>4.6199999999999998E-2</v>
+        <v>0.19369834262768532</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -3939,22 +3904,22 @@
         <v>125</v>
       </c>
       <c r="B15">
-        <v>0.32979999999999998</v>
+        <v>0.59529858872259112</v>
       </c>
       <c r="C15">
-        <v>0.61429999999999996</v>
+        <v>0.62211499455558639</v>
       </c>
       <c r="D15">
-        <v>0.81610000000000005</v>
+        <v>0.88493071716805094</v>
       </c>
       <c r="E15">
-        <v>6.4399999999999999E-2</v>
+        <v>7.7054465486687873E-2</v>
       </c>
       <c r="F15">
-        <v>4.9799999999999997E-2</v>
+        <v>2.8769989538185624E-2</v>
       </c>
       <c r="G15">
-        <v>4.1000000000000002E-2</v>
+        <v>1.3013216047142217E-2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -3962,22 +3927,22 @@
         <v>126</v>
       </c>
       <c r="B16">
-        <v>0.2387</v>
+        <v>0.34953888068022654</v>
       </c>
       <c r="C16">
-        <v>0.27960000000000002</v>
+        <v>0.66456659178169475</v>
       </c>
       <c r="D16">
-        <v>0.8821</v>
+        <v>0.89725195955112957</v>
       </c>
       <c r="E16">
-        <v>7.9100000000000004E-2</v>
+        <v>0.10525824329742883</v>
       </c>
       <c r="F16">
-        <v>6.3700000000000007E-2</v>
+        <v>4.4579444899124999E-2</v>
       </c>
       <c r="G16">
-        <v>2.0500000000000001E-2</v>
+        <v>3.5565784342266434E-2</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -3985,229 +3950,367 @@
         <v>127</v>
       </c>
       <c r="B17">
-        <v>0.2442</v>
+        <v>0.68843765953592539</v>
       </c>
       <c r="C17">
-        <v>0.31840000000000002</v>
+        <v>0.73758707573736471</v>
       </c>
       <c r="D17">
-        <v>0.88470000000000004</v>
+        <v>0.83905604136818013</v>
       </c>
       <c r="E17">
-        <v>0.15840000000000001</v>
+        <v>0.10939841575679726</v>
       </c>
       <c r="F17">
-        <v>0.17660000000000001</v>
+        <v>8.5585363042010434E-2</v>
       </c>
       <c r="G17">
-        <v>1.6500000000000001E-2</v>
+        <v>3.3677519226652172E-2</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="B18">
-        <v>0.37059999999999998</v>
+        <v>0.56334542690606348</v>
       </c>
       <c r="C18">
-        <v>0.33210000000000001</v>
+        <v>0.76253143076834695</v>
       </c>
       <c r="D18">
-        <v>0.84399999999999997</v>
+        <v>0.84796567251901311</v>
       </c>
       <c r="E18">
-        <v>3.1199999999999999E-2</v>
+        <v>0.2399741925220181</v>
       </c>
       <c r="F18">
-        <v>2.2200000000000001E-2</v>
+        <v>0.1511328333870989</v>
       </c>
       <c r="G18">
-        <v>1.3299999999999999E-2</v>
+        <v>6.0143797146152519E-2</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="B19">
-        <v>0.58989999999999998</v>
+        <v>0.79564147438462784</v>
       </c>
       <c r="C19">
-        <v>0.62770000000000004</v>
+        <v>0.8286036829750506</v>
       </c>
       <c r="D19">
-        <v>0.71689999999999998</v>
+        <v>0.86112388677509721</v>
       </c>
       <c r="E19">
-        <v>0.14480000000000001</v>
+        <v>0.11650708700924028</v>
       </c>
       <c r="F19">
-        <v>9.6199999999999994E-2</v>
+        <v>0.11181526588977356</v>
       </c>
       <c r="G19">
-        <v>3.4299999999999997E-2</v>
+        <v>2.5286855135916473E-2</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="B20">
-        <v>0.79759999999999998</v>
+        <v>0.59987250598038955</v>
       </c>
       <c r="C20">
-        <v>0.8327</v>
+        <v>0.67477195657317102</v>
       </c>
       <c r="D20">
-        <v>0.75170000000000003</v>
+        <v>0.76986672274651036</v>
       </c>
       <c r="E20">
-        <v>0.2445</v>
+        <v>0.16731947109697431</v>
       </c>
       <c r="F20">
-        <v>0.23669999999999999</v>
+        <v>9.737520044162877E-2</v>
       </c>
       <c r="G20">
-        <v>3.9800000000000002E-2</v>
+        <v>4.7139927972450778E-2</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B21">
-        <v>0.35460000000000003</v>
+        <v>0.38148459360901948</v>
       </c>
       <c r="C21">
-        <v>0.40629999999999999</v>
+        <v>0.5339087445647297</v>
       </c>
       <c r="D21">
-        <v>0.87549999999999994</v>
+        <v>0.86751401137225792</v>
       </c>
       <c r="E21">
-        <v>7.8100000000000003E-2</v>
+        <v>5.8382757242268254E-2</v>
       </c>
       <c r="F21">
-        <v>9.0999999999999998E-2</v>
+        <v>2.8451039737638583E-2</v>
       </c>
       <c r="G21">
-        <v>1.4500000000000001E-2</v>
+        <v>3.4043351634456147E-2</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="B22">
-        <v>0.55879999999999996</v>
+        <v>0.81325882556469653</v>
       </c>
       <c r="C22">
-        <v>0.60819999999999996</v>
+        <v>0.85459104447746947</v>
       </c>
       <c r="D22">
-        <v>0.77749999999999997</v>
+        <v>0.81873227018723516</v>
       </c>
       <c r="E22">
-        <v>0.19600000000000001</v>
+        <v>0.25690589885591253</v>
       </c>
       <c r="F22">
-        <v>0.1285</v>
+        <v>0.25798349629302314</v>
       </c>
       <c r="G22">
-        <v>3.5799999999999998E-2</v>
+        <v>4.4485806770313337E-2</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="B23">
-        <v>0.30680000000000002</v>
+        <v>0.39195855944745928</v>
       </c>
       <c r="C23">
-        <v>0.35870000000000002</v>
+        <v>0.44353998794057997</v>
       </c>
       <c r="D23">
-        <v>0.8931</v>
+        <v>0.95041477096237825</v>
       </c>
       <c r="E23">
-        <v>0.14630000000000001</v>
+        <v>7.6961026147015291E-2</v>
       </c>
       <c r="F23">
-        <v>8.77E-2</v>
+        <v>0.18945622978676752</v>
       </c>
       <c r="G23">
-        <v>3.0700000000000002E-2</v>
+        <v>1.3598823292952549E-2</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B24">
-        <v>0.78169999999999995</v>
+        <v>0.43180351843090026</v>
       </c>
       <c r="C24">
-        <v>0.42949999999999999</v>
+        <v>0.73450470987999483</v>
       </c>
       <c r="D24">
-        <v>0.8639</v>
+        <v>0.87640328616284568</v>
       </c>
       <c r="E24">
-        <v>9.7799999999999998E-2</v>
+        <v>0.1377120162874389</v>
       </c>
       <c r="F24">
-        <v>6.9199999999999998E-2</v>
+        <v>5.4955768706897785E-2</v>
       </c>
       <c r="G24">
-        <v>2.07E-2</v>
+        <v>5.6583078842100738E-2</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="B25">
-        <v>0.74619999999999997</v>
+        <v>0.62016829634036019</v>
       </c>
       <c r="C25">
-        <v>0.76519999999999999</v>
+        <v>0.78757544211869968</v>
       </c>
       <c r="D25">
-        <v>0.79959999999999998</v>
+        <v>0.92382050042755692</v>
       </c>
       <c r="E25">
-        <v>0.15290000000000001</v>
+        <v>0.28218140808764297</v>
       </c>
       <c r="F25">
-        <v>0.14410000000000001</v>
+        <v>0.17808677547681898</v>
       </c>
       <c r="G25">
-        <v>2.1499999999999998E-2</v>
+        <v>4.4521693869204744E-2</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="B26">
-        <v>0.83850000000000002</v>
+        <v>0.33417562217895169</v>
       </c>
       <c r="C26">
-        <v>0.83340000000000003</v>
+        <v>0.76551174002011579</v>
       </c>
       <c r="D26">
-        <v>0.75290000000000001</v>
+        <v>0.80660057176548694</v>
       </c>
       <c r="E26">
-        <v>0.2727</v>
+        <v>6.8502856350114702E-2</v>
       </c>
       <c r="F26">
-        <v>0.2344</v>
+        <v>4.7658684741194363E-2</v>
       </c>
       <c r="G26">
-        <v>6.6E-3</v>
+        <v>2.9856662257036828E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27">
+        <v>0.62724038548140137</v>
+      </c>
+      <c r="C27">
+        <v>0.57867243087453846</v>
+      </c>
+      <c r="D27">
+        <v>0.84459155183283796</v>
+      </c>
+      <c r="E27">
+        <v>5.1112311987751055E-2</v>
+      </c>
+      <c r="F27">
+        <v>1.7337656489237144E-2</v>
+      </c>
+      <c r="G27">
+        <v>1.7529046203728721E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28">
+        <v>0.74719307170829241</v>
+      </c>
+      <c r="C28">
+        <v>0.7121138624989648</v>
+      </c>
+      <c r="D28">
+        <v>0.88387776108278215</v>
+      </c>
+      <c r="E28">
+        <v>0.10044603244087408</v>
+      </c>
+      <c r="F28">
+        <v>7.7410882245069396E-2</v>
+      </c>
+      <c r="G28">
+        <v>2.6974906238538623E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29">
+        <v>0.83499607835300815</v>
+      </c>
+      <c r="C29">
+        <v>0.883914253313417</v>
+      </c>
+      <c r="D29">
+        <v>0.92466441192780169</v>
+      </c>
+      <c r="E29">
+        <v>0.20965074860993851</v>
+      </c>
+      <c r="F29">
+        <v>6.1052799856123018E-2</v>
+      </c>
+      <c r="G29">
+        <v>2.6447387483701436E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30">
+        <v>0.68416870201353264</v>
+      </c>
+      <c r="C30">
+        <v>0.77306564139720235</v>
+      </c>
+      <c r="D30">
+        <v>0.8629383786563205</v>
+      </c>
+      <c r="E30">
+        <v>0.12864755583083054</v>
+      </c>
+      <c r="F30">
+        <v>0.10300802842084351</v>
+      </c>
+      <c r="G30">
+        <v>5.0957684262191633E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31">
+        <v>0.43454212126632086</v>
+      </c>
+      <c r="C31">
+        <v>0.84847522804507247</v>
+      </c>
+      <c r="D31">
+        <v>0.8648587014845287</v>
+      </c>
+      <c r="E31">
+        <v>5.7225898765873723E-2</v>
+      </c>
+      <c r="F31">
+        <v>3.442586299409766E-2</v>
+      </c>
+      <c r="G31">
+        <v>2.5496333392952961E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32">
+        <v>0.73807576080176007</v>
+      </c>
+      <c r="C32">
+        <v>0.78867136576382746</v>
+      </c>
+      <c r="D32">
+        <v>0.86334517446051895</v>
+      </c>
+      <c r="E32">
+        <v>0.1555259216094968</v>
+      </c>
+      <c r="F32">
+        <v>0.15030387245948057</v>
+      </c>
+      <c r="G32">
+        <v>2.6584637911777998E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4217,7 +4320,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65B8A7C9-BC2A-4A40-8452-C9C3F38868A5}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -4226,288 +4329,288 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="G1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="H1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B2">
-        <v>0.62090000000000001</v>
+        <v>0.58324957112977993</v>
       </c>
       <c r="C2">
-        <v>0.14499999999999999</v>
+        <v>0.17957765278574131</v>
       </c>
       <c r="D2">
-        <v>7.1999999999999998E-3</v>
+        <v>2.7113419053212406E-3</v>
       </c>
       <c r="E2">
-        <v>2.9100000000000001E-2</v>
+        <v>2.279569992316317E-2</v>
       </c>
       <c r="F2">
-        <v>2.9000000000000001E-2</v>
+        <v>5.4621468349493833E-3</v>
       </c>
       <c r="G2">
-        <v>0.3906</v>
+        <v>3.231557419861044E-2</v>
       </c>
       <c r="H2">
-        <v>0.99980000000000002</v>
+        <v>0.99977018591727163</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="B3">
-        <v>0.39360000000000001</v>
+        <v>0.44665410506716535</v>
       </c>
       <c r="C3">
-        <v>5.5300000000000002E-2</v>
+        <v>0.1075679918545667</v>
       </c>
       <c r="D3">
-        <v>1E-4</v>
+        <v>1.0567158245730036E-3</v>
       </c>
       <c r="E3">
-        <v>2.8299999999999999E-2</v>
+        <v>4.4043347659506286E-2</v>
       </c>
       <c r="F3">
-        <v>2.24E-2</v>
+        <v>4.9712293397858581E-3</v>
       </c>
       <c r="G3">
-        <v>9.4399999999999998E-2</v>
+        <v>9.5956287256331679E-2</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.99990264422345587</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B4">
-        <v>0.35499999999999998</v>
+        <v>0.49651387621026</v>
       </c>
       <c r="C4">
-        <v>0.22339999999999999</v>
+        <v>5.3686306361996221E-2</v>
       </c>
       <c r="D4">
-        <v>6.3E-3</v>
+        <v>1.9047892871775336E-4</v>
       </c>
       <c r="E4">
-        <v>3.0700000000000002E-2</v>
+        <v>2.4629284877410635E-2</v>
       </c>
       <c r="F4">
-        <v>1.17E-2</v>
+        <v>0.11162065222860347</v>
       </c>
       <c r="G4">
-        <v>8.5199999999999998E-2</v>
+        <v>6.7627207578905002E-2</v>
       </c>
       <c r="H4">
-        <v>0.99990000000000001</v>
+        <v>0.99971607857794897</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B5">
-        <v>0.36099999999999999</v>
+        <v>0.55217175622233861</v>
       </c>
       <c r="C5">
-        <v>2.8899999999999999E-2</v>
+        <v>7.7347943808423192E-2</v>
       </c>
       <c r="D5">
-        <v>1E-4</v>
+        <v>9.7273838325892298E-4</v>
       </c>
       <c r="E5">
-        <v>1.5100000000000001E-2</v>
+        <v>2.2004395336398429E-2</v>
       </c>
       <c r="F5">
-        <v>1.84E-2</v>
+        <v>8.909840177143696E-3</v>
       </c>
       <c r="G5">
-        <v>0.22520000000000001</v>
+        <v>0.40953117335528233</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.99990023196069144</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="B6">
-        <v>0.24079999999999999</v>
+        <v>0.38661738981484844</v>
       </c>
       <c r="C6">
-        <v>9.7000000000000003E-2</v>
+        <v>6.0673854027707849E-2</v>
       </c>
       <c r="D6">
-        <v>2.0000000000000001E-4</v>
+        <v>2.3358058270569364E-4</v>
       </c>
       <c r="E6">
-        <v>2.5899999999999999E-2</v>
+        <v>2.7853186817750047E-2</v>
       </c>
       <c r="F6">
-        <v>1.9300000000000001E-2</v>
+        <v>2.5112507980669909E-2</v>
       </c>
       <c r="G6">
-        <v>6.8599999999999994E-2</v>
+        <v>0.13867419661256247</v>
       </c>
       <c r="H6">
-        <v>0.99990000000000001</v>
+        <v>0.99985985165037661</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="B7">
-        <v>0.54920000000000002</v>
+        <v>0.62285737204393798</v>
       </c>
       <c r="C7">
-        <v>0.1004</v>
+        <v>0.15636985305545389</v>
       </c>
       <c r="D7">
-        <v>3.7000000000000002E-3</v>
+        <v>1.5842537212415336E-3</v>
       </c>
       <c r="E7">
-        <v>3.7100000000000001E-2</v>
+        <v>2.5483422990730111E-2</v>
       </c>
       <c r="F7">
-        <v>7.4999999999999997E-3</v>
+        <v>1.6018008352426266E-2</v>
       </c>
       <c r="G7">
-        <v>5.8799999999999998E-2</v>
+        <v>0.42678090673458235</v>
       </c>
       <c r="H7">
-        <v>0.99990000000000001</v>
+        <v>0.99983956924341855</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="B8">
-        <v>0.63049999999999995</v>
+        <v>0.32834233349697267</v>
       </c>
       <c r="C8">
-        <v>6.0600000000000001E-2</v>
+        <v>6.1719303987345223E-2</v>
       </c>
       <c r="D8">
-        <v>2.7699999999999999E-2</v>
+        <v>1.5156119721657277E-3</v>
       </c>
       <c r="E8">
-        <v>2.1299999999999999E-2</v>
+        <v>1.777434914401041E-2</v>
       </c>
       <c r="F8">
-        <v>3.5999999999999999E-3</v>
+        <v>9.1209450561438778E-3</v>
       </c>
       <c r="G8">
-        <v>7.0999999999999994E-2</v>
+        <v>6.228814549874933E-2</v>
       </c>
       <c r="H8">
-        <v>0.99990000000000001</v>
+        <v>0.9999064918063445</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="B9">
-        <v>0.62339999999999995</v>
+        <v>0.46760022718815486</v>
       </c>
       <c r="C9">
-        <v>0.3856</v>
+        <v>7.4208268865430194E-2</v>
       </c>
       <c r="D9">
-        <v>0.12709999999999999</v>
+        <v>5.1313186705575901E-4</v>
       </c>
       <c r="E9">
-        <v>4.1399999999999999E-2</v>
+        <v>8.319395209463562E-2</v>
       </c>
       <c r="F9">
-        <v>9.7000000000000003E-3</v>
+        <v>8.6566521083452485E-3</v>
       </c>
       <c r="G9">
-        <v>5.9900000000000002E-2</v>
+        <v>3.5155408449049137E-2</v>
       </c>
       <c r="H9">
-        <v>0.99970000000000003</v>
+        <v>0.99985898666248851</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="B10">
-        <v>0.33019999999999999</v>
+        <v>0.36150325856272653</v>
       </c>
       <c r="C10">
-        <v>4.5900000000000003E-2</v>
+        <v>3.6755085048174138E-2</v>
       </c>
       <c r="D10">
-        <v>1E-4</v>
+        <v>4.382312984793374E-5</v>
       </c>
       <c r="E10">
-        <v>4.3299999999999998E-2</v>
+        <v>1.0461207139413897E-2</v>
       </c>
       <c r="F10">
-        <v>6.4999999999999997E-3</v>
+        <v>1.5338095446776809E-2</v>
       </c>
       <c r="G10">
-        <v>4.87E-2</v>
+        <v>0.17235010924480226</v>
       </c>
       <c r="H10">
-        <v>0.99980000000000002</v>
+        <v>0.99990609329318303</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B11">
-        <v>0.4108</v>
+        <v>0.36074698135588068</v>
       </c>
       <c r="C11">
-        <v>8.2299999999999998E-2</v>
+        <v>0.21155057722471574</v>
       </c>
       <c r="D11">
-        <v>1.1999999999999999E-3</v>
+        <v>1.7575265149704761E-3</v>
       </c>
       <c r="E11">
-        <v>3.6400000000000002E-2</v>
+        <v>2.3834145112164518E-2</v>
       </c>
       <c r="F11">
-        <v>6.3E-3</v>
+        <v>1.377996376323576E-2</v>
       </c>
       <c r="G11">
-        <v>7.0599999999999996E-2</v>
+        <v>0.10597298318944355</v>
       </c>
       <c r="H11">
-        <v>0.99990000000000001</v>
+        <v>0.99993482596359817</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -4515,25 +4618,25 @@
         <v>122</v>
       </c>
       <c r="B12">
-        <v>0.45900000000000002</v>
+        <v>0.27665848069452087</v>
       </c>
       <c r="C12">
-        <v>8.3799999999999999E-2</v>
+        <v>2.9444859674915606E-2</v>
       </c>
       <c r="D12">
-        <v>3.8E-3</v>
+        <v>1.0677354972772745E-4</v>
       </c>
       <c r="E12">
-        <v>6.4199999999999993E-2</v>
+        <v>1.4578696212824324E-2</v>
       </c>
       <c r="F12">
-        <v>1.09E-2</v>
+        <v>1.6673100457483592E-2</v>
       </c>
       <c r="G12">
-        <v>3.5499999999999997E-2</v>
+        <v>0.11323745616124449</v>
       </c>
       <c r="H12">
-        <v>0.99990000000000001</v>
+        <v>0.99960575920100536</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -4541,25 +4644,25 @@
         <v>123</v>
       </c>
       <c r="B13">
-        <v>0.40039999999999998</v>
+        <v>0.23429358797705643</v>
       </c>
       <c r="C13">
-        <v>6.0100000000000001E-2</v>
+        <v>0.29507482295638798</v>
       </c>
       <c r="D13">
-        <v>1E-4</v>
+        <v>2.9031947960393503E-3</v>
       </c>
       <c r="E13">
-        <v>2.0299999999999999E-2</v>
+        <v>7.9571890921908542E-2</v>
       </c>
       <c r="F13">
-        <v>1.15E-2</v>
+        <v>3.4351267343865157E-3</v>
       </c>
       <c r="G13">
-        <v>7.1199999999999999E-2</v>
+        <v>3.4658890633511713E-2</v>
       </c>
       <c r="H13">
-        <v>0.99990000000000001</v>
+        <v>0.99990386772198547</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -4567,25 +4670,25 @@
         <v>124</v>
       </c>
       <c r="B14">
-        <v>0.47360000000000002</v>
+        <v>0.79469311292854483</v>
       </c>
       <c r="C14">
-        <v>3.9899999999999998E-2</v>
+        <v>0.11474983304857636</v>
       </c>
       <c r="D14">
-        <v>2.5000000000000001E-3</v>
+        <v>7.3285170377180122E-4</v>
       </c>
       <c r="E14">
-        <v>2.06E-2</v>
+        <v>0.17158703589672428</v>
       </c>
       <c r="F14">
-        <v>8.0000000000000002E-3</v>
+        <v>7.6320650807004155E-3</v>
       </c>
       <c r="G14">
-        <v>3.4299999999999997E-2</v>
+        <v>5.1559803300868144E-2</v>
       </c>
       <c r="H14">
-        <v>0.99990000000000001</v>
+        <v>0.99930617590175452</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -4593,25 +4696,25 @@
         <v>125</v>
       </c>
       <c r="B15">
-        <v>0.32840000000000003</v>
+        <v>0.48913252343232916</v>
       </c>
       <c r="C15">
-        <v>6.2799999999999995E-2</v>
+        <v>6.4148002647479552E-2</v>
       </c>
       <c r="D15">
-        <v>6.4999999999999997E-3</v>
+        <v>6.4051924760339052E-5</v>
       </c>
       <c r="E15">
-        <v>1.8100000000000002E-2</v>
+        <v>1.4283579221555608E-2</v>
       </c>
       <c r="F15">
-        <v>1.01E-2</v>
+        <v>6.1062834938189888E-3</v>
       </c>
       <c r="G15">
-        <v>6.8000000000000005E-2</v>
+        <v>9.3409056942161117E-2</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0.999807844225719</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -4619,25 +4722,25 @@
         <v>126</v>
       </c>
       <c r="B16">
-        <v>0.51129999999999998</v>
+        <v>0.4395491521886003</v>
       </c>
       <c r="C16">
-        <v>5.5599999999999997E-2</v>
+        <v>3.2325041058569572E-2</v>
       </c>
       <c r="D16">
-        <v>5.9999999999999995E-4</v>
+        <v>5.4927852266048547E-4</v>
       </c>
       <c r="E16">
-        <v>2.47E-2</v>
+        <v>3.6581949609188334E-2</v>
       </c>
       <c r="F16">
-        <v>1.0200000000000001E-2</v>
+        <v>7.3713177741037148E-3</v>
       </c>
       <c r="G16">
-        <v>0.4113</v>
+        <v>0.13605079727777564</v>
       </c>
       <c r="H16">
-        <v>0.99980000000000002</v>
+        <v>0.99982423087274863</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -4645,259 +4748,415 @@
         <v>127</v>
       </c>
       <c r="B17">
-        <v>0.60760000000000003</v>
+        <v>0.35544192480608666</v>
       </c>
       <c r="C17">
-        <v>0.1608</v>
+        <v>5.4320438713502298E-2</v>
       </c>
       <c r="D17">
-        <v>1.6000000000000001E-3</v>
+        <v>1.646822456071011E-4</v>
       </c>
       <c r="E17">
-        <v>1.78E-2</v>
+        <v>3.352107109332543E-2</v>
       </c>
       <c r="F17">
-        <v>8.5000000000000006E-3</v>
+        <v>1.6427053999308334E-2</v>
       </c>
       <c r="G17">
-        <v>3.15E-2</v>
+        <v>2.8926436440887309E-2</v>
       </c>
       <c r="H17">
-        <v>0.99929999999999997</v>
+        <v>0.99981061541755178</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="B18">
-        <v>0.49969999999999998</v>
+        <v>0.55904123451661802</v>
       </c>
       <c r="C18">
-        <v>1.7399999999999999E-2</v>
+        <v>0.14855650467760539</v>
       </c>
       <c r="D18">
-        <v>1E-4</v>
+        <v>2.6514532173175246E-4</v>
       </c>
       <c r="E18">
-        <v>2.1000000000000001E-2</v>
+        <v>4.2489537807513335E-2</v>
       </c>
       <c r="F18">
-        <v>7.7999999999999996E-3</v>
+        <v>1.3641726803098666E-2</v>
       </c>
       <c r="G18">
-        <v>0.13569999999999999</v>
+        <v>0.10212072066498447</v>
       </c>
       <c r="H18">
-        <v>0.99990000000000001</v>
+        <v>0.99983207462956991</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="B19">
-        <v>0.49330000000000002</v>
+        <v>0.26402917231616485</v>
       </c>
       <c r="C19">
-        <v>5.9400000000000001E-2</v>
+        <v>0.10785215537065686</v>
       </c>
       <c r="D19">
-        <v>6.9999999999999999E-4</v>
+        <v>3.8526093215226467E-4</v>
       </c>
       <c r="E19">
-        <v>5.9700000000000003E-2</v>
+        <v>2.2957370429879522E-2</v>
       </c>
       <c r="F19">
-        <v>2.1700000000000001E-2</v>
+        <v>1.3558795596676602E-2</v>
       </c>
       <c r="G19">
-        <v>5.5100000000000003E-2</v>
+        <v>8.9950961360419066E-2</v>
       </c>
       <c r="H19">
-        <v>0.99980000000000002</v>
+        <v>0.99985366057615921</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="B20">
-        <v>0.50290000000000001</v>
+        <v>0.51405062958387004</v>
       </c>
       <c r="C20">
-        <v>0.24179999999999999</v>
+        <v>6.4292473909728975E-2</v>
       </c>
       <c r="D20">
-        <v>6.1999999999999998E-3</v>
+        <v>5.9146710128545521E-4</v>
       </c>
       <c r="E20">
-        <v>4.7100000000000003E-2</v>
+        <v>5.4717278725585551E-2</v>
       </c>
       <c r="F20">
-        <v>1.3299999999999999E-2</v>
+        <v>2.0865644962014668E-2</v>
       </c>
       <c r="G20">
-        <v>6.7900000000000002E-2</v>
+        <v>6.4607923030414557E-2</v>
       </c>
       <c r="H20">
-        <v>0.99960000000000004</v>
+        <v>0.9997634131594858</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B21">
-        <v>0.72589999999999999</v>
+        <v>0.48693495623230731</v>
       </c>
       <c r="C21">
-        <v>9.7299999999999998E-2</v>
+        <v>2.0427642581518857E-2</v>
       </c>
       <c r="D21">
-        <v>2.9999999999999997E-4</v>
+        <v>4.1605821551815564E-4</v>
       </c>
       <c r="E21">
-        <v>1.47E-2</v>
+        <v>3.3129655161161377E-2</v>
       </c>
       <c r="F21">
-        <v>4.0000000000000002E-4</v>
+        <v>6.5345613849027975E-3</v>
       </c>
       <c r="G21">
-        <v>0.16209999999999999</v>
+        <v>0.1211993897812839</v>
       </c>
       <c r="H21">
-        <v>0.99929999999999997</v>
+        <v>0.99979604989435389</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="B22">
-        <v>0.57930000000000004</v>
+        <v>0.51469763699765092</v>
       </c>
       <c r="C22">
-        <v>0.14119999999999999</v>
+        <v>0.26258986057931805</v>
       </c>
       <c r="D22">
-        <v>2.3999999999999998E-3</v>
+        <v>5.446348362031052E-3</v>
       </c>
       <c r="E22">
-        <v>2.7199999999999998E-2</v>
+        <v>4.1157135383339136E-2</v>
       </c>
       <c r="F22">
-        <v>2.1299999999999999E-2</v>
+        <v>7.0116784882787832E-3</v>
       </c>
       <c r="G22">
-        <v>8.5900000000000004E-2</v>
+        <v>8.8946601607850409E-2</v>
       </c>
       <c r="H22">
-        <v>0.99980000000000002</v>
+        <v>0.99991245823528307</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="B23">
-        <v>0.38169999999999998</v>
+        <v>0.76432512927332863</v>
       </c>
       <c r="C23">
-        <v>9.2600000000000002E-2</v>
+        <v>0.20646732079884522</v>
       </c>
       <c r="D23">
-        <v>2.3999999999999998E-3</v>
+        <v>3.6086900911765242E-4</v>
       </c>
       <c r="E23">
-        <v>2.4299999999999999E-2</v>
+        <v>1.2397449249940616E-2</v>
       </c>
       <c r="F23">
-        <v>1.78E-2</v>
+        <v>3.928447441027609E-4</v>
       </c>
       <c r="G23">
-        <v>9.7000000000000003E-2</v>
+        <v>0.137788010012973</v>
       </c>
       <c r="H23">
-        <v>0.99990000000000001</v>
+        <v>0.99978987374152639</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B24">
-        <v>0.40400000000000003</v>
+        <v>0.44662136005849712</v>
       </c>
       <c r="C24">
-        <v>7.1199999999999999E-2</v>
+        <v>4.8439359398970566E-2</v>
       </c>
       <c r="D24">
-        <v>4.4999999999999997E-3</v>
+        <v>4.1578849269502632E-4</v>
       </c>
       <c r="E24">
-        <v>2.75E-2</v>
+        <v>8.7975110040575219E-2</v>
       </c>
       <c r="F24">
-        <v>1.2200000000000001E-2</v>
+        <v>1.3441438341434041E-2</v>
       </c>
       <c r="G24">
-        <v>6.3500000000000001E-2</v>
+        <v>0.11444219823074828</v>
       </c>
       <c r="H24">
-        <v>0.99990000000000001</v>
+        <v>0.99992831232884571</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="B25">
-        <v>0.37580000000000002</v>
+        <v>0.43955645611034688</v>
       </c>
       <c r="C25">
-        <v>0.13600000000000001</v>
+        <v>0.17857629723265295</v>
       </c>
       <c r="D25">
-        <v>2.9999999999999997E-4</v>
+        <v>4.4273834752326779E-3</v>
       </c>
       <c r="E25">
-        <v>3.3399999999999999E-2</v>
+        <v>3.1945941926608913E-2</v>
       </c>
       <c r="F25">
-        <v>1.5800000000000002E-2</v>
+        <v>1.0335725173811205E-2</v>
       </c>
       <c r="G25">
-        <v>7.2999999999999995E-2</v>
+        <v>8.5808826263152019E-2</v>
       </c>
       <c r="H25">
-        <v>0.99990000000000001</v>
+        <v>0.99983269509610739</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="B26">
-        <v>0.93759999999999999</v>
+        <v>0.25024401603321589</v>
       </c>
       <c r="C26">
-        <v>0.31509999999999999</v>
+        <v>5.3539842739717881E-2</v>
       </c>
       <c r="D26">
-        <v>1E-4</v>
+        <v>5.623516704569665E-3</v>
       </c>
       <c r="E26">
-        <v>0.1183</v>
+        <v>1.9476690894857578E-2</v>
       </c>
       <c r="F26">
-        <v>8.6999999999999994E-3</v>
+        <v>5.8217023153033978E-3</v>
       </c>
       <c r="G26">
-        <v>4.8800000000000003E-2</v>
+        <v>7.1901739574198209E-2</v>
       </c>
       <c r="H26">
-        <v>0.99980000000000002</v>
+        <v>0.9997968597489979</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27">
+        <v>0.32343735927226874</v>
+      </c>
+      <c r="C27">
+        <v>1.2485364315950645E-2</v>
+      </c>
+      <c r="D27">
+        <v>1.6887327749256958E-4</v>
+      </c>
+      <c r="E27">
+        <v>2.0929028190579124E-2</v>
+      </c>
+      <c r="F27">
+        <v>2.2741601368999369E-2</v>
+      </c>
+      <c r="G27">
+        <v>0.14179726200126092</v>
+      </c>
+      <c r="H27">
+        <v>0.99931324867153026</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28">
+        <v>0.39659422090239738</v>
+      </c>
+      <c r="C28">
+        <v>7.1258710646806195E-2</v>
+      </c>
+      <c r="D28">
+        <v>5.4383619448749648E-3</v>
+      </c>
+      <c r="E28">
+        <v>2.452981239820325E-2</v>
+      </c>
+      <c r="F28">
+        <v>6.5425978727683591E-3</v>
+      </c>
+      <c r="G28">
+        <v>8.2565297808486052E-2</v>
+      </c>
+      <c r="H28">
+        <v>0.99979098391364873</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29">
+        <v>0.46030144226686182</v>
+      </c>
+      <c r="C29">
+        <v>6.0348402116190657E-2</v>
+      </c>
+      <c r="D29">
+        <v>1.5087100529047664E-3</v>
+      </c>
+      <c r="E29">
+        <v>2.6062716377497241E-2</v>
+      </c>
+      <c r="F29">
+        <v>1.5586673394247918E-2</v>
+      </c>
+      <c r="G29">
+        <v>0.47189153273950774</v>
+      </c>
+      <c r="H29">
+        <v>0.99992006834156799</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30">
+        <v>0.56471234413527949</v>
+      </c>
+      <c r="C30">
+        <v>8.003295508992532E-2</v>
+      </c>
+      <c r="D30">
+        <v>1.0517581891061223E-3</v>
+      </c>
+      <c r="E30">
+        <v>4.2356639515723785E-2</v>
+      </c>
+      <c r="F30">
+        <v>2.1438337754613127E-2</v>
+      </c>
+      <c r="G30">
+        <v>6.8925219992754555E-2</v>
+      </c>
+      <c r="H30">
+        <v>0.99938063128863752</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31">
+        <v>0.46604811303881238</v>
+      </c>
+      <c r="C31">
+        <v>3.5659989268467182E-2</v>
+      </c>
+      <c r="D31">
+        <v>2.5308531568592378E-3</v>
+      </c>
+      <c r="E31">
+        <v>2.4624396351278843E-2</v>
+      </c>
+      <c r="F31">
+        <v>9.3498479699517089E-3</v>
+      </c>
+      <c r="G31">
+        <v>3.4314076193883027E-2</v>
+      </c>
+      <c r="H31">
+        <v>0.99964228223931317</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32">
+        <v>0.37946143415847688</v>
+      </c>
+      <c r="C32">
+        <v>0.13680424039355873</v>
+      </c>
+      <c r="D32">
+        <v>2.652113659879497E-4</v>
+      </c>
+      <c r="E32">
+        <v>2.9049983004060347E-2</v>
+      </c>
+      <c r="F32">
+        <v>1.1542297477503726E-2</v>
+      </c>
+      <c r="G32">
+        <v>0.12108579774458278</v>
+      </c>
+      <c r="H32">
+        <v>0.99962272749345371</v>
       </c>
     </row>
   </sheetData>
@@ -4921,68 +5180,68 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="F1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="G1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>0.59789999999999999</v>
+        <v>0.29299999999999998</v>
       </c>
       <c r="C2">
-        <v>0.64739999999999998</v>
+        <v>0.58220000000000005</v>
       </c>
       <c r="D2">
-        <v>0.81859999999999999</v>
+        <v>0.86070000000000002</v>
       </c>
       <c r="E2">
-        <v>8.6599999999999996E-2</v>
+        <v>0.1002</v>
       </c>
       <c r="F2">
-        <v>9.0700000000000003E-2</v>
+        <v>2.75E-2</v>
       </c>
       <c r="G2">
-        <v>1.24E-2</v>
+        <v>6.6900000000000001E-2</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>0.53220000000000001</v>
+        <v>0.53469999999999995</v>
       </c>
       <c r="C3">
-        <v>0.49940000000000001</v>
+        <v>0.53469999999999995</v>
       </c>
       <c r="D3">
-        <v>0.85119999999999996</v>
+        <v>0.90529999999999999</v>
       </c>
       <c r="E3">
-        <v>7.5999999999999998E-2</v>
+        <v>3.8300000000000001E-2</v>
       </c>
       <c r="F3">
-        <v>1.6799999999999999E-2</v>
+        <v>1.49E-2</v>
       </c>
       <c r="G3">
         <v>1.9E-3</v>
@@ -4990,85 +5249,85 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>0.34849999999999998</v>
+        <v>0.58979999999999999</v>
       </c>
       <c r="C4">
-        <v>0.4289</v>
+        <v>0.68899999999999995</v>
       </c>
       <c r="D4">
-        <v>0.81859999999999999</v>
+        <v>0.81230000000000002</v>
       </c>
       <c r="E4">
-        <v>9.4799999999999995E-2</v>
+        <v>6.7000000000000004E-2</v>
       </c>
       <c r="F4">
-        <v>8.2000000000000007E-3</v>
+        <v>9.6500000000000002E-2</v>
       </c>
       <c r="G4">
-        <v>6.1899999999999997E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>0.71299999999999997</v>
+        <v>0.69069999999999998</v>
       </c>
       <c r="C5">
-        <v>0.70220000000000005</v>
+        <v>0.68720000000000003</v>
       </c>
       <c r="D5">
-        <v>0.83909999999999996</v>
+        <v>0.88939999999999997</v>
       </c>
       <c r="E5">
-        <v>0.14779999999999999</v>
+        <v>0.19409999999999999</v>
       </c>
       <c r="F5">
-        <v>4.3499999999999997E-2</v>
+        <v>3.1600000000000003E-2</v>
       </c>
       <c r="G5">
-        <v>1.9599999999999999E-2</v>
+        <v>1.35E-2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>0.59850000000000003</v>
+        <v>7.8100000000000003E-2</v>
       </c>
       <c r="C6">
-        <v>0.71589999999999998</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="D6">
-        <v>0.10100000000000001</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0.54290000000000005</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0.8548</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>9.7199999999999995E-2</v>
+        <v>7.7999999999999996E-3</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>6.9800000000000001E-2</v>
+        <v>6.5100000000000005E-2</v>
       </c>
       <c r="C7">
-        <v>6.9800000000000001E-2</v>
+        <v>5.62E-2</v>
       </c>
       <c r="D7">
-        <v>8.3999999999999995E-3</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5082,157 +5341,157 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>0.27379999999999999</v>
+        <v>0.64239999999999997</v>
       </c>
       <c r="C8">
-        <v>0.31890000000000002</v>
+        <v>0.93759999999999999</v>
       </c>
       <c r="D8">
-        <v>0.70709999999999995</v>
+        <v>0.51749999999999996</v>
       </c>
       <c r="E8">
-        <v>9.9400000000000002E-2</v>
+        <v>0.65010000000000001</v>
       </c>
       <c r="F8">
-        <v>5.3199999999999997E-2</v>
+        <v>0.94350000000000001</v>
       </c>
       <c r="G8">
-        <v>4.7800000000000002E-2</v>
+        <v>0.11210000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>0.42799999999999999</v>
+        <v>0.62990000000000002</v>
       </c>
       <c r="C9">
-        <v>0.68720000000000003</v>
+        <v>0.76849999999999996</v>
       </c>
       <c r="D9">
-        <v>0.1502</v>
+        <v>0.1638</v>
       </c>
       <c r="E9">
-        <v>0.54530000000000001</v>
+        <v>0.59209999999999996</v>
       </c>
       <c r="F9">
-        <v>0.36630000000000001</v>
+        <v>0.89129999999999998</v>
       </c>
       <c r="G9">
-        <v>0.40329999999999999</v>
+        <v>9.1300000000000006E-2</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B10">
-        <v>0.629</v>
+        <v>0.74880000000000002</v>
       </c>
       <c r="C10">
-        <v>0.92359999999999998</v>
+        <v>0.80569999999999997</v>
       </c>
       <c r="D10">
-        <v>0.46350000000000002</v>
+        <v>0.93359999999999999</v>
       </c>
       <c r="E10">
-        <v>0.61380000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="F10">
-        <v>0.97109999999999996</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="G10">
-        <v>9.8500000000000004E-2</v>
+        <v>7.1099999999999997E-2</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>0.57979999999999998</v>
+        <v>0.3947</v>
       </c>
       <c r="C11">
-        <v>0.84509999999999996</v>
+        <v>0.48680000000000001</v>
       </c>
       <c r="D11">
-        <v>0.9143</v>
+        <v>0.87309999999999999</v>
       </c>
       <c r="E11">
-        <v>0.88149999999999995</v>
+        <v>7.5300000000000006E-2</v>
       </c>
       <c r="F11">
-        <v>0.98</v>
+        <v>9.3399999999999997E-2</v>
       </c>
       <c r="G11">
-        <v>4.58E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B12">
-        <v>0.42170000000000002</v>
+        <v>0.5847</v>
       </c>
       <c r="C12">
-        <v>0.66269999999999996</v>
+        <v>0.79179999999999995</v>
       </c>
       <c r="D12">
-        <v>0.78310000000000002</v>
+        <v>0.95920000000000005</v>
       </c>
       <c r="E12">
-        <v>1.2E-2</v>
+        <v>0.93920000000000003</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>0.98509999999999998</v>
       </c>
       <c r="G12">
-        <v>1.2E-2</v>
+        <v>3.78E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B13">
-        <v>7.6899999999999996E-2</v>
+        <v>0.46</v>
       </c>
       <c r="C13">
-        <v>2.1999999999999999E-2</v>
+        <v>0.78</v>
       </c>
       <c r="D13">
-        <v>5.4999999999999997E-3</v>
+        <v>0.82</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="F13">
-        <v>1.0999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>2.1999999999999999E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B14">
-        <v>0.75</v>
+        <v>0.752</v>
       </c>
       <c r="C14">
-        <v>0.73209999999999997</v>
+        <v>0.90400000000000003</v>
       </c>
       <c r="D14">
-        <v>0.71430000000000005</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="E14">
-        <v>5.3600000000000002E-2</v>
+        <v>8.7999999999999995E-2</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -5243,42 +5502,42 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B15">
-        <v>0.65610000000000002</v>
+        <v>0.41710000000000003</v>
       </c>
       <c r="C15">
-        <v>0.66669999999999996</v>
+        <v>0.79139999999999999</v>
       </c>
       <c r="D15">
-        <v>0.89949999999999997</v>
+        <v>0.12570000000000001</v>
       </c>
       <c r="E15">
-        <v>9.5200000000000007E-2</v>
+        <v>0.5857</v>
       </c>
       <c r="F15">
-        <v>1.06E-2</v>
+        <v>0.33139999999999997</v>
       </c>
       <c r="G15">
-        <v>3.6999999999999998E-2</v>
+        <v>0.48570000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B16">
-        <v>0.63219999999999998</v>
+        <v>0.97829999999999995</v>
       </c>
       <c r="C16">
-        <v>0.71260000000000001</v>
+        <v>0.95650000000000002</v>
       </c>
       <c r="D16">
-        <v>0.91949999999999998</v>
+        <v>0.97929999999999995</v>
       </c>
       <c r="E16">
-        <v>0.21840000000000001</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -5302,169 +5561,169 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="F1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="G1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="H1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>0.42270000000000002</v>
+        <v>0.6492</v>
       </c>
       <c r="C2">
-        <v>7.4200000000000002E-2</v>
+        <v>4.3200000000000002E-2</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="E2">
-        <v>1.24E-2</v>
+        <v>9.7600000000000006E-2</v>
       </c>
       <c r="F2">
-        <v>3.09E-2</v>
+        <v>1.5299999999999999E-2</v>
       </c>
       <c r="G2">
-        <v>0.11550000000000001</v>
+        <v>0.1565</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0.99429999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>0.7571</v>
+        <v>0.72160000000000002</v>
       </c>
       <c r="C3">
-        <v>5.8000000000000003E-2</v>
+        <v>4.02E-2</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>1.2999999999999999E-3</v>
       </c>
-      <c r="E3">
-        <v>5.7999999999999996E-3</v>
-      </c>
       <c r="F3">
-        <v>4.7699999999999999E-2</v>
+        <v>1.95E-2</v>
       </c>
       <c r="G3">
-        <v>0.14369999999999999</v>
+        <v>0.14149999999999999</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.99480000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>0.52370000000000005</v>
+        <v>0.38069999999999998</v>
       </c>
       <c r="C4">
-        <v>3.09E-2</v>
+        <v>6.9699999999999998E-2</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5.1499999999999997E-2</v>
+        <v>1.34E-2</v>
       </c>
       <c r="F4">
-        <v>3.7100000000000001E-2</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="G4">
-        <v>0.2268</v>
+        <v>0.1019</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.98929999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>0.64570000000000005</v>
+        <v>0.5847</v>
       </c>
       <c r="C5">
-        <v>6.3E-2</v>
+        <v>1.8100000000000002E-2</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0.05</v>
+        <v>2.93E-2</v>
       </c>
       <c r="F5">
-        <v>6.5199999999999994E-2</v>
+        <v>2.7099999999999999E-2</v>
       </c>
       <c r="G5">
-        <v>7.6100000000000001E-2</v>
+        <v>6.5500000000000003E-2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.99550000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>0.98609999999999998</v>
+        <v>0.41410000000000002</v>
       </c>
       <c r="C6">
-        <v>0.73860000000000003</v>
+        <v>3.9100000000000003E-2</v>
       </c>
       <c r="D6">
-        <v>1.2999999999999999E-3</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="E6">
-        <v>8.4599999999999995E-2</v>
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="F6">
-        <v>6.5699999999999995E-2</v>
+        <v>4.6899999999999997E-2</v>
       </c>
       <c r="G6">
-        <v>0.18060000000000001</v>
+        <v>6.25E-2</v>
       </c>
       <c r="H6">
-        <v>0.99870000000000003</v>
+        <v>0.99219999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>0.25700000000000001</v>
+        <v>0.1154</v>
       </c>
       <c r="C7">
-        <v>5.5999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -5473,166 +5732,166 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>4.7500000000000001E-2</v>
+        <v>3.2500000000000001E-2</v>
       </c>
       <c r="G7">
-        <v>5.5899999999999998E-2</v>
+        <v>2.9600000000000001E-2</v>
       </c>
       <c r="H7">
-        <v>0.99719999999999998</v>
+        <v>0.99409999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>0.73540000000000005</v>
+        <v>0.99909999999999999</v>
       </c>
       <c r="C8">
-        <v>7.3400000000000007E-2</v>
+        <v>0.9153</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="E8">
-        <v>7.8E-2</v>
+        <v>9.4100000000000003E-2</v>
       </c>
       <c r="F8">
-        <v>4.5499999999999999E-2</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="G8">
-        <v>0.11890000000000001</v>
+        <v>0.1009</v>
       </c>
       <c r="H8">
-        <v>0.99429999999999996</v>
+        <v>0.99909999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>0.9486</v>
+        <v>0.99209999999999998</v>
       </c>
       <c r="C9">
-        <v>0.31890000000000002</v>
+        <v>0.78269999999999995</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1.6000000000000001E-3</v>
       </c>
       <c r="E9">
-        <v>0.41770000000000002</v>
+        <v>8.3500000000000005E-2</v>
       </c>
       <c r="F9">
-        <v>8.2299999999999998E-2</v>
+        <v>6.7699999999999996E-2</v>
       </c>
       <c r="G9">
-        <v>0.1132</v>
+        <v>0.1386</v>
       </c>
       <c r="H9">
-        <v>0.99790000000000001</v>
+        <v>0.99839999999999995</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="C10">
-        <v>0.94230000000000003</v>
+        <v>9.4999999999999998E-3</v>
       </c>
       <c r="D10">
-        <v>7.5600000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>7.8899999999999998E-2</v>
+        <v>9.4999999999999998E-3</v>
       </c>
       <c r="F10">
-        <v>9.2999999999999992E-3</v>
+        <v>2.8400000000000002E-2</v>
       </c>
       <c r="G10">
-        <v>7.9799999999999996E-2</v>
+        <v>0.14219999999999999</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>0.99529999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>0.99880000000000002</v>
+        <v>0.6179</v>
       </c>
       <c r="C11">
-        <v>0.91779999999999995</v>
+        <v>7.1099999999999997E-2</v>
       </c>
       <c r="D11">
-        <v>0.16200000000000001</v>
+        <v>1.4E-3</v>
       </c>
       <c r="E11">
-        <v>1.41E-2</v>
+        <v>3.6299999999999999E-2</v>
       </c>
       <c r="F11">
-        <v>6.4600000000000005E-2</v>
+        <v>2.0899999999999998E-2</v>
       </c>
       <c r="G11">
-        <v>0.1643</v>
+        <v>9.2100000000000001E-2</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0.99860000000000004</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B12">
-        <v>0.21690000000000001</v>
+        <v>0.999</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>0.92230000000000001</v>
       </c>
       <c r="D12">
-        <v>1.2E-2</v>
+        <v>0.1096</v>
       </c>
       <c r="E12">
-        <v>2.41E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="F12">
-        <v>2.41E-2</v>
+        <v>7.0699999999999999E-2</v>
       </c>
       <c r="G12">
-        <v>2.41E-2</v>
+        <v>0.1265</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0.999</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B13">
-        <v>0.28570000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="C13">
-        <v>3.85E-2</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>5.4999999999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>2.1999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>6.0400000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>0.2802</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -5640,10 +5899,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B14">
-        <v>0.26790000000000003</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -5655,47 +5914,47 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>3.5700000000000003E-2</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="G14">
-        <v>0.26790000000000003</v>
+        <v>0.152</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0.96799999999999997</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B15">
-        <v>0.51849999999999996</v>
+        <v>0.99139999999999995</v>
       </c>
       <c r="C15">
-        <v>3.6999999999999998E-2</v>
+        <v>0.38</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>3.1699999999999999E-2</v>
+        <v>0.44</v>
       </c>
       <c r="F15">
-        <v>2.6499999999999999E-2</v>
+        <v>2.86E-2</v>
       </c>
       <c r="G15">
-        <v>0.1852</v>
+        <v>0.1686</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0.99709999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B16">
-        <v>0.2989</v>
+        <v>2.1700000000000001E-2</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -5707,10 +5966,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2.1700000000000001E-2</v>
       </c>
       <c r="G16">
-        <v>0.22989999999999999</v>
+        <v>0.28260000000000002</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -5719,4 +5978,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{fd60f3b8-f236-4830-aecc-da0a7fc54679}" enabled="1" method="Standard" siteId="{76f33c20-5979-4408-adf7-8b3c4be95e52}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>